--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-es-ES]#,##0"/>
+    <numFmt numFmtId="165" formatCode="[$-es-ES]#,##0.00"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -69,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,6 +86,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -114,6 +123,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -144,6 +156,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -597,7 +612,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -630,7 +645,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="N7" s="7" t="n">
         <v>8369</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -676,7 +691,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -709,7 +724,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="N8" s="7" t="n">
         <v>6069</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
@@ -755,7 +770,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -788,7 +803,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="N9" s="7" t="n">
         <v>4386</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -834,7 +849,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -867,7 +882,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N10" s="4" t="n">
+      <c r="N10" s="7" t="n">
         <v>3296</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
@@ -913,7 +928,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -946,7 +961,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="N11" s="7" t="n">
         <v>2410</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -992,7 +1007,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1025,7 +1040,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="N12" s="7" t="n">
         <v>1656</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
@@ -1071,7 +1086,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1104,7 +1119,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N13" s="4" t="n">
+      <c r="N13" s="7" t="n">
         <v>1087</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1150,7 +1165,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1183,7 +1198,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N14" s="4" t="n">
+      <c r="N14" s="7" t="n">
         <v>717</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
@@ -1229,7 +1244,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1262,7 +1277,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N15" s="4" t="n">
+      <c r="N15" s="7" t="n">
         <v>532</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1308,7 +1323,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1341,7 +1356,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N16" s="4" t="n">
+      <c r="N16" s="7" t="n">
         <v>403</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
@@ -1387,7 +1402,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1420,7 +1435,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N17" s="4" t="n">
+      <c r="N17" s="7" t="n">
         <v>305</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1466,7 +1481,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1499,7 +1514,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N18" s="4" t="n">
+      <c r="N18" s="7" t="n">
         <v>215</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
@@ -1545,7 +1560,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1578,7 +1593,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N19" s="4" t="n">
+      <c r="N19" s="7" t="n">
         <v>173</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -1624,7 +1639,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1657,7 +1672,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N20" s="4" t="n">
+      <c r="N20" s="7" t="n">
         <v>171</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
@@ -1703,7 +1718,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1736,7 +1751,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N21" s="4" t="n">
+      <c r="N21" s="7" t="n">
         <v>173</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -1782,7 +1797,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1815,7 +1830,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N22" s="4" t="n">
+      <c r="N22" s="7" t="n">
         <v>186</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
@@ -1861,7 +1876,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1894,7 +1909,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N23" s="4" t="n">
+      <c r="N23" s="7" t="n">
         <v>190</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -1940,7 +1955,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1973,7 +1988,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N24" s="4" t="n">
+      <c r="N24" s="7" t="n">
         <v>196</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
@@ -2019,7 +2034,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2052,7 +2067,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N25" s="4" t="n">
+      <c r="N25" s="7" t="n">
         <v>205</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -2098,7 +2113,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2131,7 +2146,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N26" s="4" t="n">
+      <c r="N26" s="7" t="n">
         <v>228</v>
       </c>
       <c r="O26" s="4" t="inlineStr">
@@ -2177,7 +2192,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2210,7 +2225,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N27" s="4" t="n">
+      <c r="N27" s="7" t="n">
         <v>237</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2256,7 +2271,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2289,7 +2304,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N28" s="4" t="n">
+      <c r="N28" s="7" t="n">
         <v>251</v>
       </c>
       <c r="O28" s="4" t="inlineStr">
@@ -2335,7 +2350,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2368,7 +2383,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N29" s="4" t="n">
+      <c r="N29" s="7" t="n">
         <v>260</v>
       </c>
       <c r="O29" s="4" t="inlineStr">
@@ -2414,7 +2429,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2447,7 +2462,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N30" s="4" t="n">
+      <c r="N30" s="7" t="n">
         <v>260</v>
       </c>
       <c r="O30" s="4" t="inlineStr">
@@ -2493,7 +2508,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2526,7 +2541,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N31" s="4" t="n">
+      <c r="N31" s="7" t="n">
         <v>247</v>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -2572,7 +2587,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2605,7 +2620,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N32" s="4" t="n">
+      <c r="N32" s="7" t="n">
         <v>237</v>
       </c>
       <c r="O32" s="4" t="inlineStr">
@@ -2651,7 +2666,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2684,7 +2699,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N33" s="4" t="n">
+      <c r="N33" s="7" t="n">
         <v>201</v>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -2730,7 +2745,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2763,7 +2778,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N34" s="4" t="n">
+      <c r="N34" s="7" t="n">
         <v>182</v>
       </c>
       <c r="O34" s="4" t="inlineStr">
@@ -2809,7 +2824,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2842,7 +2857,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N35" s="4" t="n">
+      <c r="N35" s="7" t="n">
         <v>137</v>
       </c>
       <c r="O35" s="4" t="inlineStr">
@@ -2888,7 +2903,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2921,7 +2936,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N36" s="4" t="n">
+      <c r="N36" s="7" t="n">
         <v>32</v>
       </c>
       <c r="O36" s="4" t="inlineStr">
@@ -2967,7 +2982,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -3000,7 +3015,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N37" s="4" t="n">
+      <c r="N37" s="7" t="n">
         <v>-69</v>
       </c>
       <c r="O37" s="4" t="inlineStr">
@@ -3046,7 +3061,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -3079,7 +3094,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N38" s="4" t="n">
+      <c r="N38" s="7" t="n">
         <v>-236</v>
       </c>
       <c r="O38" s="4" t="inlineStr">
@@ -3125,7 +3140,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -3158,7 +3173,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N39" s="4" t="n">
+      <c r="N39" s="7" t="n">
         <v>-381</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -3204,7 +3219,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3237,7 +3252,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N40" s="4" t="n">
+      <c r="N40" s="7" t="n">
         <v>-477</v>
       </c>
       <c r="O40" s="4" t="inlineStr">
@@ -3283,7 +3298,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3316,7 +3331,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N41" s="4" t="n">
+      <c r="N41" s="7" t="n">
         <v>-559</v>
       </c>
       <c r="O41" s="4" t="inlineStr">
@@ -3362,7 +3377,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3395,7 +3410,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N42" s="4" t="n">
+      <c r="N42" s="7" t="n">
         <v>-622</v>
       </c>
       <c r="O42" s="4" t="inlineStr">
@@ -3441,7 +3456,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3474,7 +3489,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N43" s="4" t="n">
+      <c r="N43" s="7" t="n">
         <v>-708</v>
       </c>
       <c r="O43" s="4" t="inlineStr">
@@ -3520,7 +3535,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3553,7 +3568,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N44" s="4" t="n">
+      <c r="N44" s="7" t="n">
         <v>-816</v>
       </c>
       <c r="O44" s="4" t="inlineStr">
@@ -3599,7 +3614,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G45" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3632,7 +3647,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N45" s="4" t="n">
+      <c r="N45" s="7" t="n">
         <v>-1010</v>
       </c>
       <c r="O45" s="4" t="inlineStr">
@@ -3678,7 +3693,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G46" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3711,7 +3726,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N46" s="4" t="n">
+      <c r="N46" s="7" t="n">
         <v>-1376</v>
       </c>
       <c r="O46" s="4" t="inlineStr">
@@ -3757,7 +3772,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="G47" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3790,7 +3805,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N47" s="4" t="n">
+      <c r="N47" s="7" t="n">
         <v>-1999</v>
       </c>
       <c r="O47" s="4" t="inlineStr">
@@ -3836,7 +3851,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="G48" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3869,7 +3884,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N48" s="4" t="n">
+      <c r="N48" s="7" t="n">
         <v>-2856</v>
       </c>
       <c r="O48" s="4" t="inlineStr">
@@ -3915,7 +3930,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="G49" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3948,7 +3963,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N49" s="4" t="n">
+      <c r="N49" s="7" t="n">
         <v>-3944</v>
       </c>
       <c r="O49" s="4" t="inlineStr">
@@ -3994,7 +4009,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -4027,7 +4042,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N50" s="4" t="n">
+      <c r="N50" s="7" t="n">
         <v>-5729</v>
       </c>
       <c r="O50" s="4" t="inlineStr">
@@ -4073,7 +4088,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -4106,7 +4121,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N51" s="4" t="n">
+      <c r="N51" s="7" t="n">
         <v>-10798</v>
       </c>
       <c r="O51" s="4" t="inlineStr">
@@ -4152,7 +4167,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4185,7 +4200,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N52" s="4" t="n">
+      <c r="N52" s="7" t="n">
         <v>-18407</v>
       </c>
       <c r="O52" s="4" t="inlineStr">
@@ -4231,7 +4246,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="G53" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4264,7 +4279,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N53" s="4" t="n">
+      <c r="N53" s="7" t="n">
         <v>-27240</v>
       </c>
       <c r="O53" s="4" t="inlineStr">
@@ -4310,7 +4325,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="G54" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4343,7 +4358,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N54" s="4" t="n">
+      <c r="N54" s="7" t="n">
         <v>-36060</v>
       </c>
       <c r="O54" s="4" t="inlineStr">
@@ -4389,7 +4404,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="G55" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4422,7 +4437,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N55" s="4" t="n">
+      <c r="N55" s="7" t="n">
         <v>-43636</v>
       </c>
       <c r="O55" s="4" t="inlineStr">
@@ -4468,7 +4483,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4501,7 +4516,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N56" s="4" t="n">
+      <c r="N56" s="7" t="n">
         <v>-50286</v>
       </c>
       <c r="O56" s="4" t="inlineStr">
@@ -4547,7 +4562,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4580,7 +4595,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N57" s="4" t="n">
+      <c r="N57" s="7" t="n">
         <v>-52781</v>
       </c>
       <c r="O57" s="4" t="inlineStr">
@@ -4626,7 +4641,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4659,7 +4674,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N58" s="4" t="n">
+      <c r="N58" s="7" t="n">
         <v>-54384</v>
       </c>
       <c r="O58" s="4" t="inlineStr">
@@ -4705,7 +4720,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="G59" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -4738,7 +4753,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N59" s="4" t="n">
+      <c r="N59" s="7" t="n">
         <v>-55131</v>
       </c>
       <c r="O59" s="4" t="inlineStr">
@@ -4784,7 +4799,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="G60" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -4817,7 +4832,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N60" s="4" t="n">
+      <c r="N60" s="7" t="n">
         <v>-57818</v>
       </c>
       <c r="O60" s="4" t="inlineStr">
@@ -4863,7 +4878,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="G61" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -4896,7 +4911,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N61" s="4" t="n">
+      <c r="N61" s="7" t="n">
         <v>-62437</v>
       </c>
       <c r="O61" s="4" t="inlineStr">
@@ -4942,7 +4957,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="G62" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -4975,7 +4990,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N62" s="4" t="n">
+      <c r="N62" s="7" t="n">
         <v>-77417</v>
       </c>
       <c r="O62" s="4" t="inlineStr">
@@ -5021,7 +5036,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="G63" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -5054,7 +5069,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N63" s="4" t="n">
+      <c r="N63" s="7" t="n">
         <v>-283270</v>
       </c>
       <c r="O63" s="4" t="inlineStr">
@@ -5100,7 +5115,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="G64" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -5133,7 +5148,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N64" s="4" t="n">
+      <c r="N64" s="7" t="n">
         <v>-817376</v>
       </c>
       <c r="O64" s="4" t="inlineStr">
@@ -5179,7 +5194,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="G65" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5212,7 +5227,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N65" s="4" t="n">
+      <c r="N65" s="7" t="n">
         <v>-1355602</v>
       </c>
       <c r="O65" s="4" t="inlineStr">
@@ -5258,7 +5273,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="G66" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -5291,7 +5306,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N66" s="4" t="n">
+      <c r="N66" s="7" t="n">
         <v>-975534</v>
       </c>
       <c r="O66" s="4" t="inlineStr">
@@ -5337,7 +5352,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="G67" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -5370,7 +5385,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N67" s="4" t="n">
+      <c r="N67" s="7" t="n">
         <v>-524649</v>
       </c>
       <c r="O67" s="4" t="inlineStr">
@@ -5416,7 +5431,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="G68" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -5449,7 +5464,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N68" s="4" t="n">
+      <c r="N68" s="7" t="n">
         <v>-332936</v>
       </c>
       <c r="O68" s="4" t="inlineStr">
@@ -5495,7 +5510,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="G69" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -5528,7 +5543,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N69" s="4" t="n">
+      <c r="N69" s="7" t="n">
         <v>-141107</v>
       </c>
       <c r="O69" s="4" t="inlineStr">
@@ -5574,7 +5589,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="G70" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -5607,7 +5622,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N70" s="4" t="n">
+      <c r="N70" s="7" t="n">
         <v>-112899</v>
       </c>
       <c r="O70" s="4" t="inlineStr">
@@ -5653,7 +5668,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="G71" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -5686,7 +5701,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N71" s="4" t="n">
+      <c r="N71" s="7" t="n">
         <v>-105297</v>
       </c>
       <c r="O71" s="4" t="inlineStr">
@@ -5732,7 +5747,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="G72" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -5765,7 +5780,7 @@
           <t>Migración neta</t>
         </is>
       </c>
-      <c r="N72" s="4" t="n">
+      <c r="N72" s="7" t="n">
         <v>-100467</v>
       </c>
       <c r="O72" s="4" t="inlineStr">
@@ -5811,7 +5826,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -5844,7 +5859,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N73" s="4" t="n">
+      <c r="N73" s="8" t="n">
         <v>60.397</v>
       </c>
       <c r="O73" s="4" t="inlineStr">
@@ -5890,7 +5905,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="G74" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -5923,7 +5938,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N74" s="4" t="n">
+      <c r="N74" s="8" t="n">
         <v>61.08</v>
       </c>
       <c r="O74" s="4" t="inlineStr">
@@ -5969,7 +5984,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="G75" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -6002,7 +6017,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N75" s="4" t="n">
+      <c r="N75" s="8" t="n">
         <v>61.711</v>
       </c>
       <c r="O75" s="4" t="inlineStr">
@@ -6048,7 +6063,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -6081,7 +6096,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N76" s="4" t="n">
+      <c r="N76" s="8" t="n">
         <v>62.414</v>
       </c>
       <c r="O76" s="4" t="inlineStr">
@@ -6127,7 +6142,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="G77" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -6160,7 +6175,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N77" s="4" t="n">
+      <c r="N77" s="8" t="n">
         <v>63.075</v>
       </c>
       <c r="O77" s="4" t="inlineStr">
@@ -6206,7 +6221,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="G78" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -6239,7 +6254,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N78" s="4" t="n">
+      <c r="N78" s="8" t="n">
         <v>63.748</v>
       </c>
       <c r="O78" s="4" t="inlineStr">
@@ -6285,7 +6300,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="G79" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -6318,7 +6333,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N79" s="4" t="n">
+      <c r="N79" s="8" t="n">
         <v>64.84699999999999</v>
       </c>
       <c r="O79" s="4" t="inlineStr">
@@ -6364,7 +6379,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="G80" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -6397,7 +6412,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N80" s="4" t="n">
+      <c r="N80" s="8" t="n">
         <v>65.377</v>
       </c>
       <c r="O80" s="4" t="inlineStr">
@@ -6443,7 +6458,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G81" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -6476,7 +6491,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N81" s="4" t="n">
+      <c r="N81" s="8" t="n">
         <v>65.828</v>
       </c>
       <c r="O81" s="4" t="inlineStr">
@@ -6522,7 +6537,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="G82" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -6555,7 +6570,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N82" s="4" t="n">
+      <c r="N82" s="8" t="n">
         <v>65.541</v>
       </c>
       <c r="O82" s="4" t="inlineStr">
@@ -6601,7 +6616,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="G83" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -6634,7 +6649,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N83" s="4" t="n">
+      <c r="N83" s="8" t="n">
         <v>66.783</v>
       </c>
       <c r="O83" s="4" t="inlineStr">
@@ -6680,7 +6695,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="G84" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -6713,7 +6728,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N84" s="4" t="n">
+      <c r="N84" s="8" t="n">
         <v>67.15900000000001</v>
       </c>
       <c r="O84" s="4" t="inlineStr">
@@ -6759,7 +6774,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="G85" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -6792,7 +6807,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N85" s="4" t="n">
+      <c r="N85" s="8" t="n">
         <v>67.625</v>
       </c>
       <c r="O85" s="4" t="inlineStr">
@@ -6838,7 +6853,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G86" s="4" t="n">
+      <c r="G86" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -6871,7 +6886,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N86" s="4" t="n">
+      <c r="N86" s="8" t="n">
         <v>67.931</v>
       </c>
       <c r="O86" s="4" t="inlineStr">
@@ -6917,7 +6932,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="G87" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -6950,7 +6965,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N87" s="4" t="n">
+      <c r="N87" s="8" t="n">
         <v>68.494</v>
       </c>
       <c r="O87" s="4" t="inlineStr">
@@ -6996,7 +7011,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="G88" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -7029,7 +7044,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N88" s="4" t="n">
+      <c r="N88" s="8" t="n">
         <v>69.038</v>
       </c>
       <c r="O88" s="4" t="inlineStr">
@@ -7075,7 +7090,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G89" s="4" t="n">
+      <c r="G89" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -7108,7 +7123,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N89" s="4" t="n">
+      <c r="N89" s="8" t="n">
         <v>69.608</v>
       </c>
       <c r="O89" s="4" t="inlineStr">
@@ -7154,7 +7169,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G90" s="4" t="n">
+      <c r="G90" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -7187,7 +7202,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N90" s="4" t="n">
+      <c r="N90" s="8" t="n">
         <v>70.298</v>
       </c>
       <c r="O90" s="4" t="inlineStr">
@@ -7233,7 +7248,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G91" s="4" t="n">
+      <c r="G91" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -7266,7 +7281,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N91" s="4" t="n">
+      <c r="N91" s="8" t="n">
         <v>70.874</v>
       </c>
       <c r="O91" s="4" t="inlineStr">
@@ -7312,7 +7327,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G92" s="4" t="n">
+      <c r="G92" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -7345,7 +7360,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N92" s="4" t="n">
+      <c r="N92" s="8" t="n">
         <v>71.011</v>
       </c>
       <c r="O92" s="4" t="inlineStr">
@@ -7391,7 +7406,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="G93" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -7424,7 +7439,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N93" s="4" t="n">
+      <c r="N93" s="8" t="n">
         <v>71.068</v>
       </c>
       <c r="O93" s="4" t="inlineStr">
@@ -7470,7 +7485,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="G94" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -7503,7 +7518,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N94" s="4" t="n">
+      <c r="N94" s="8" t="n">
         <v>71.52500000000001</v>
       </c>
       <c r="O94" s="4" t="inlineStr">
@@ -7549,7 +7564,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G95" s="4" t="n">
+      <c r="G95" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -7582,7 +7597,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N95" s="4" t="n">
+      <c r="N95" s="8" t="n">
         <v>71.89400000000001</v>
       </c>
       <c r="O95" s="4" t="inlineStr">
@@ -7628,7 +7643,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G96" s="4" t="n">
+      <c r="G96" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -7661,7 +7676,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N96" s="4" t="n">
+      <c r="N96" s="8" t="n">
         <v>72.373</v>
       </c>
       <c r="O96" s="4" t="inlineStr">
@@ -7707,7 +7722,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G97" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -7740,7 +7755,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N97" s="4" t="n">
+      <c r="N97" s="8" t="n">
         <v>72.37</v>
       </c>
       <c r="O97" s="4" t="inlineStr">
@@ -7786,7 +7801,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G98" s="4" t="n">
+      <c r="G98" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -7819,7 +7834,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N98" s="4" t="n">
+      <c r="N98" s="8" t="n">
         <v>72.569</v>
       </c>
       <c r="O98" s="4" t="inlineStr">
@@ -7865,7 +7880,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G99" s="4" t="n">
+      <c r="G99" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -7898,7 +7913,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N99" s="4" t="n">
+      <c r="N99" s="8" t="n">
         <v>73.123</v>
       </c>
       <c r="O99" s="4" t="inlineStr">
@@ -7944,7 +7959,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G100" s="4" t="n">
+      <c r="G100" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -7977,7 +7992,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N100" s="4" t="n">
+      <c r="N100" s="8" t="n">
         <v>73.371</v>
       </c>
       <c r="O100" s="4" t="inlineStr">
@@ -8023,7 +8038,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G101" s="4" t="n">
+      <c r="G101" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -8056,7 +8071,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N101" s="4" t="n">
+      <c r="N101" s="8" t="n">
         <v>73.551</v>
       </c>
       <c r="O101" s="4" t="inlineStr">
@@ -8102,7 +8117,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G102" s="4" t="n">
+      <c r="G102" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -8135,7 +8150,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N102" s="4" t="n">
+      <c r="N102" s="8" t="n">
         <v>73.77500000000001</v>
       </c>
       <c r="O102" s="4" t="inlineStr">
@@ -8181,7 +8196,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G103" s="4" t="n">
+      <c r="G103" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -8214,7 +8229,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N103" s="4" t="n">
+      <c r="N103" s="8" t="n">
         <v>73.687</v>
       </c>
       <c r="O103" s="4" t="inlineStr">
@@ -8260,7 +8275,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G104" s="4" t="n">
+      <c r="G104" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -8293,7 +8308,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N104" s="4" t="n">
+      <c r="N104" s="8" t="n">
         <v>74.23099999999999</v>
       </c>
       <c r="O104" s="4" t="inlineStr">
@@ -8339,7 +8354,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G105" s="4" t="n">
+      <c r="G105" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -8372,7 +8387,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N105" s="4" t="n">
+      <c r="N105" s="8" t="n">
         <v>74.41200000000001</v>
       </c>
       <c r="O105" s="4" t="inlineStr">
@@ -8418,7 +8433,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G106" s="4" t="n">
+      <c r="G106" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -8451,7 +8466,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N106" s="4" t="n">
+      <c r="N106" s="8" t="n">
         <v>74.768</v>
       </c>
       <c r="O106" s="4" t="inlineStr">
@@ -8497,7 +8512,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G107" s="4" t="n">
+      <c r="G107" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -8530,7 +8545,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N107" s="4" t="n">
+      <c r="N107" s="8" t="n">
         <v>74.637</v>
       </c>
       <c r="O107" s="4" t="inlineStr">
@@ -8576,7 +8591,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G108" s="4" t="n">
+      <c r="G108" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -8609,7 +8624,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N108" s="4" t="n">
+      <c r="N108" s="8" t="n">
         <v>74.929</v>
       </c>
       <c r="O108" s="4" t="inlineStr">
@@ -8655,7 +8670,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G109" s="4" t="n">
+      <c r="G109" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -8688,7 +8703,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N109" s="4" t="n">
+      <c r="N109" s="8" t="n">
         <v>75.09099999999999</v>
       </c>
       <c r="O109" s="4" t="inlineStr">
@@ -8734,7 +8749,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G110" s="4" t="n">
+      <c r="G110" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -8767,7 +8782,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N110" s="4" t="n">
+      <c r="N110" s="8" t="n">
         <v>75.669</v>
       </c>
       <c r="O110" s="4" t="inlineStr">
@@ -8813,7 +8828,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G111" s="4" t="n">
+      <c r="G111" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -8846,7 +8861,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N111" s="4" t="n">
+      <c r="N111" s="8" t="n">
         <v>75.80500000000001</v>
       </c>
       <c r="O111" s="4" t="inlineStr">
@@ -8892,7 +8907,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G112" s="4" t="n">
+      <c r="G112" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -8925,7 +8940,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N112" s="4" t="n">
+      <c r="N112" s="8" t="n">
         <v>75.444</v>
       </c>
       <c r="O112" s="4" t="inlineStr">
@@ -8971,7 +8986,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G113" s="4" t="n">
+      <c r="G113" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -9004,7 +9019,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N113" s="4" t="n">
+      <c r="N113" s="8" t="n">
         <v>76.244</v>
       </c>
       <c r="O113" s="4" t="inlineStr">
@@ -9050,7 +9065,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G114" s="4" t="n">
+      <c r="G114" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -9083,7 +9098,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N114" s="4" t="n">
+      <c r="N114" s="8" t="n">
         <v>75.34999999999999</v>
       </c>
       <c r="O114" s="4" t="inlineStr">
@@ -9129,7 +9144,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G115" s="4" t="n">
+      <c r="G115" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -9162,7 +9177,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N115" s="4" t="n">
+      <c r="N115" s="8" t="n">
         <v>76.86499999999999</v>
       </c>
       <c r="O115" s="4" t="inlineStr">
@@ -9208,7 +9223,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G116" s="4" t="n">
+      <c r="G116" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -9241,7 +9256,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N116" s="4" t="n">
+      <c r="N116" s="8" t="n">
         <v>76.161</v>
       </c>
       <c r="O116" s="4" t="inlineStr">
@@ -9287,7 +9302,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G117" s="4" t="n">
+      <c r="G117" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -9320,7 +9335,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N117" s="4" t="n">
+      <c r="N117" s="8" t="n">
         <v>76.702</v>
       </c>
       <c r="O117" s="4" t="inlineStr">
@@ -9366,7 +9381,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G118" s="4" t="n">
+      <c r="G118" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -9399,7 +9414,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N118" s="4" t="n">
+      <c r="N118" s="8" t="n">
         <v>76.967</v>
       </c>
       <c r="O118" s="4" t="inlineStr">
@@ -9445,7 +9460,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G119" s="4" t="n">
+      <c r="G119" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -9478,7 +9493,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N119" s="4" t="n">
+      <c r="N119" s="8" t="n">
         <v>77.184</v>
       </c>
       <c r="O119" s="4" t="inlineStr">
@@ -9524,7 +9539,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G120" s="4" t="n">
+      <c r="G120" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -9557,7 +9572,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N120" s="4" t="n">
+      <c r="N120" s="8" t="n">
         <v>77.664</v>
       </c>
       <c r="O120" s="4" t="inlineStr">
@@ -9603,7 +9618,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G121" s="4" t="n">
+      <c r="G121" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -9636,7 +9651,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N121" s="4" t="n">
+      <c r="N121" s="8" t="n">
         <v>77.20399999999999</v>
       </c>
       <c r="O121" s="4" t="inlineStr">
@@ -9682,7 +9697,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G122" s="4" t="n">
+      <c r="G122" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
@@ -9715,7 +9730,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N122" s="4" t="n">
+      <c r="N122" s="8" t="n">
         <v>77.315</v>
       </c>
       <c r="O122" s="4" t="inlineStr">
@@ -9761,7 +9776,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G123" s="4" t="n">
+      <c r="G123" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
@@ -9794,7 +9809,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N123" s="4" t="n">
+      <c r="N123" s="8" t="n">
         <v>77.36199999999999</v>
       </c>
       <c r="O123" s="4" t="inlineStr">
@@ -9840,7 +9855,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G124" s="4" t="n">
+      <c r="G124" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -9873,7 +9888,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N124" s="4" t="n">
+      <c r="N124" s="8" t="n">
         <v>77.786</v>
       </c>
       <c r="O124" s="4" t="inlineStr">
@@ -9919,7 +9934,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G125" s="4" t="n">
+      <c r="G125" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -9952,7 +9967,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N125" s="4" t="n">
+      <c r="N125" s="8" t="n">
         <v>77.63200000000001</v>
       </c>
       <c r="O125" s="4" t="inlineStr">
@@ -9998,7 +10013,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G126" s="4" t="n">
+      <c r="G126" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -10031,7 +10046,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N126" s="4" t="n">
+      <c r="N126" s="8" t="n">
         <v>77.473</v>
       </c>
       <c r="O126" s="4" t="inlineStr">
@@ -10077,7 +10092,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G127" s="4" t="n">
+      <c r="G127" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -10110,7 +10125,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N127" s="4" t="n">
+      <c r="N127" s="8" t="n">
         <v>77.339</v>
       </c>
       <c r="O127" s="4" t="inlineStr">
@@ -10156,7 +10171,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G128" s="4" t="n">
+      <c r="G128" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -10189,7 +10204,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N128" s="4" t="n">
+      <c r="N128" s="8" t="n">
         <v>77.395</v>
       </c>
       <c r="O128" s="4" t="inlineStr">
@@ -10235,7 +10250,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G129" s="4" t="n">
+      <c r="G129" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -10268,7 +10283,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N129" s="4" t="n">
+      <c r="N129" s="8" t="n">
         <v>76.79300000000001</v>
       </c>
       <c r="O129" s="4" t="inlineStr">
@@ -10314,7 +10329,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G130" s="4" t="n">
+      <c r="G130" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -10347,7 +10362,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N130" s="4" t="n">
+      <c r="N130" s="8" t="n">
         <v>76.306</v>
       </c>
       <c r="O130" s="4" t="inlineStr">
@@ -10393,7 +10408,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G131" s="4" t="n">
+      <c r="G131" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -10426,7 +10441,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N131" s="4" t="n">
+      <c r="N131" s="8" t="n">
         <v>76.554</v>
       </c>
       <c r="O131" s="4" t="inlineStr">
@@ -10472,7 +10487,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G132" s="4" t="n">
+      <c r="G132" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -10505,7 +10520,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N132" s="4" t="n">
+      <c r="N132" s="8" t="n">
         <v>76.67700000000001</v>
       </c>
       <c r="O132" s="4" t="inlineStr">
@@ -10551,7 +10566,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G133" s="4" t="n">
+      <c r="G133" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
@@ -10584,7 +10599,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N133" s="4" t="n">
+      <c r="N133" s="8" t="n">
         <v>76.501</v>
       </c>
       <c r="O133" s="4" t="inlineStr">
@@ -10630,7 +10645,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G134" s="4" t="n">
+      <c r="G134" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -10663,7 +10678,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N134" s="4" t="n">
+      <c r="N134" s="8" t="n">
         <v>75.619</v>
       </c>
       <c r="O134" s="4" t="inlineStr">
@@ -10709,7 +10724,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G135" s="4" t="n">
+      <c r="G135" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -10742,7 +10757,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N135" s="4" t="n">
+      <c r="N135" s="8" t="n">
         <v>76.52500000000001</v>
       </c>
       <c r="O135" s="4" t="inlineStr">
@@ -10788,7 +10803,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G136" s="4" t="n">
+      <c r="G136" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -10821,7 +10836,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N136" s="4" t="n">
+      <c r="N136" s="8" t="n">
         <v>76.501</v>
       </c>
       <c r="O136" s="4" t="inlineStr">
@@ -10867,7 +10882,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G137" s="4" t="n">
+      <c r="G137" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
@@ -10900,7 +10915,7 @@
           <t>Esperanza de vida femenina</t>
         </is>
       </c>
-      <c r="N137" s="4" t="n">
+      <c r="N137" s="8" t="n">
         <v>76.655</v>
       </c>
       <c r="O137" s="4" t="inlineStr">
@@ -10946,7 +10961,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G138" s="4" t="n">
+      <c r="G138" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -11023,7 +11038,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G139" s="4" t="n">
+      <c r="G139" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -11056,7 +11071,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N139" s="4" t="n">
+      <c r="N139" s="8" t="n">
         <v>58.376</v>
       </c>
       <c r="O139" s="4" t="inlineStr">
@@ -11102,7 +11117,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G140" s="4" t="n">
+      <c r="G140" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
@@ -11135,7 +11150,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N140" s="4" t="n">
+      <c r="N140" s="8" t="n">
         <v>59.115</v>
       </c>
       <c r="O140" s="4" t="inlineStr">
@@ -11181,7 +11196,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G141" s="4" t="n">
+      <c r="G141" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -11214,7 +11229,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N141" s="4" t="n">
+      <c r="N141" s="8" t="n">
         <v>59.667</v>
       </c>
       <c r="O141" s="4" t="inlineStr">
@@ -11260,7 +11275,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G142" s="4" t="n">
+      <c r="G142" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -11293,7 +11308,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N142" s="4" t="n">
+      <c r="N142" s="8" t="n">
         <v>60.502</v>
       </c>
       <c r="O142" s="4" t="inlineStr">
@@ -11339,7 +11354,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G143" s="4" t="n">
+      <c r="G143" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
@@ -11372,7 +11387,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N143" s="4" t="n">
+      <c r="N143" s="8" t="n">
         <v>61.168</v>
       </c>
       <c r="O143" s="4" t="inlineStr">
@@ -11418,7 +11433,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G144" s="4" t="n">
+      <c r="G144" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
@@ -11451,7 +11466,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N144" s="4" t="n">
+      <c r="N144" s="8" t="n">
         <v>61.909</v>
       </c>
       <c r="O144" s="4" t="inlineStr">
@@ -11497,7 +11512,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G145" s="4" t="n">
+      <c r="G145" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -11530,7 +11545,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N145" s="4" t="n">
+      <c r="N145" s="8" t="n">
         <v>62.894</v>
       </c>
       <c r="O145" s="4" t="inlineStr">
@@ -11576,7 +11591,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G146" s="4" t="n">
+      <c r="G146" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -11609,7 +11624,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N146" s="4" t="n">
+      <c r="N146" s="8" t="n">
         <v>63.55</v>
       </c>
       <c r="O146" s="4" t="inlineStr">
@@ -11655,7 +11670,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G147" s="4" t="n">
+      <c r="G147" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -11688,7 +11703,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N147" s="4" t="n">
+      <c r="N147" s="8" t="n">
         <v>63.908</v>
       </c>
       <c r="O147" s="4" t="inlineStr">
@@ -11734,7 +11749,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G148" s="4" t="n">
+      <c r="G148" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -11767,7 +11782,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N148" s="4" t="n">
+      <c r="N148" s="8" t="n">
         <v>63.84</v>
       </c>
       <c r="O148" s="4" t="inlineStr">
@@ -11813,7 +11828,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G149" s="4" t="n">
+      <c r="G149" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
@@ -11846,7 +11861,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N149" s="4" t="n">
+      <c r="N149" s="8" t="n">
         <v>64.816</v>
       </c>
       <c r="O149" s="4" t="inlineStr">
@@ -11892,7 +11907,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G150" s="4" t="n">
+      <c r="G150" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
@@ -11925,7 +11940,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N150" s="4" t="n">
+      <c r="N150" s="8" t="n">
         <v>65.184</v>
       </c>
       <c r="O150" s="4" t="inlineStr">
@@ -11971,7 +11986,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G151" s="4" t="n">
+      <c r="G151" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
@@ -12004,7 +12019,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N151" s="4" t="n">
+      <c r="N151" s="8" t="n">
         <v>65.55500000000001</v>
       </c>
       <c r="O151" s="4" t="inlineStr">
@@ -12050,7 +12065,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G152" s="4" t="n">
+      <c r="G152" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
@@ -12083,7 +12098,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N152" s="4" t="n">
+      <c r="N152" s="8" t="n">
         <v>65.73999999999999</v>
       </c>
       <c r="O152" s="4" t="inlineStr">
@@ -12129,7 +12144,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G153" s="4" t="n">
+      <c r="G153" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
@@ -12162,7 +12177,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N153" s="4" t="n">
+      <c r="N153" s="8" t="n">
         <v>66.223</v>
       </c>
       <c r="O153" s="4" t="inlineStr">
@@ -12208,7 +12223,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G154" s="4" t="n">
+      <c r="G154" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
@@ -12241,7 +12256,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N154" s="4" t="n">
+      <c r="N154" s="8" t="n">
         <v>66.68600000000001</v>
       </c>
       <c r="O154" s="4" t="inlineStr">
@@ -12287,7 +12302,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G155" s="4" t="n">
+      <c r="G155" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
@@ -12320,7 +12335,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N155" s="4" t="n">
+      <c r="N155" s="8" t="n">
         <v>67.26600000000001</v>
       </c>
       <c r="O155" s="4" t="inlineStr">
@@ -12366,7 +12381,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G156" s="4" t="n">
+      <c r="G156" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
@@ -12399,7 +12414,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N156" s="4" t="n">
+      <c r="N156" s="8" t="n">
         <v>67.726</v>
       </c>
       <c r="O156" s="4" t="inlineStr">
@@ -12445,7 +12460,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G157" s="4" t="n">
+      <c r="G157" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
@@ -12478,7 +12493,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N157" s="4" t="n">
+      <c r="N157" s="8" t="n">
         <v>68.108</v>
       </c>
       <c r="O157" s="4" t="inlineStr">
@@ -12524,7 +12539,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G158" s="4" t="n">
+      <c r="G158" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
@@ -12557,7 +12572,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N158" s="4" t="n">
+      <c r="N158" s="8" t="n">
         <v>68.226</v>
       </c>
       <c r="O158" s="4" t="inlineStr">
@@ -12603,7 +12618,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G159" s="4" t="n">
+      <c r="G159" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
@@ -12636,7 +12651,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N159" s="4" t="n">
+      <c r="N159" s="8" t="n">
         <v>68.179</v>
       </c>
       <c r="O159" s="4" t="inlineStr">
@@ -12682,7 +12697,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G160" s="4" t="n">
+      <c r="G160" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
@@ -12715,7 +12730,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N160" s="4" t="n">
+      <c r="N160" s="8" t="n">
         <v>68.697</v>
       </c>
       <c r="O160" s="4" t="inlineStr">
@@ -12761,7 +12776,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G161" s="4" t="n">
+      <c r="G161" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
@@ -12794,7 +12809,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N161" s="4" t="n">
+      <c r="N161" s="8" t="n">
         <v>68.985</v>
       </c>
       <c r="O161" s="4" t="inlineStr">
@@ -12840,7 +12855,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G162" s="4" t="n">
+      <c r="G162" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
@@ -12873,7 +12888,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N162" s="4" t="n">
+      <c r="N162" s="8" t="n">
         <v>69.541</v>
       </c>
       <c r="O162" s="4" t="inlineStr">
@@ -12919,7 +12934,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G163" s="4" t="n">
+      <c r="G163" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -12952,7 +12967,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N163" s="4" t="n">
+      <c r="N163" s="8" t="n">
         <v>69.672</v>
       </c>
       <c r="O163" s="4" t="inlineStr">
@@ -12998,7 +13013,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G164" s="4" t="n">
+      <c r="G164" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -13031,7 +13046,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N164" s="4" t="n">
+      <c r="N164" s="8" t="n">
         <v>69.961</v>
       </c>
       <c r="O164" s="4" t="inlineStr">
@@ -13077,7 +13092,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G165" s="4" t="n">
+      <c r="G165" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
@@ -13110,7 +13125,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N165" s="4" t="n">
+      <c r="N165" s="8" t="n">
         <v>70.52800000000001</v>
       </c>
       <c r="O165" s="4" t="inlineStr">
@@ -13156,7 +13171,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G166" s="4" t="n">
+      <c r="G166" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -13189,7 +13204,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N166" s="4" t="n">
+      <c r="N166" s="8" t="n">
         <v>70.673</v>
       </c>
       <c r="O166" s="4" t="inlineStr">
@@ -13235,7 +13250,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G167" s="4" t="n">
+      <c r="G167" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
@@ -13268,7 +13283,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N167" s="4" t="n">
+      <c r="N167" s="8" t="n">
         <v>70.762</v>
       </c>
       <c r="O167" s="4" t="inlineStr">
@@ -13314,7 +13329,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G168" s="4" t="n">
+      <c r="G168" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -13347,7 +13362,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N168" s="4" t="n">
+      <c r="N168" s="8" t="n">
         <v>70.80500000000001</v>
       </c>
       <c r="O168" s="4" t="inlineStr">
@@ -13393,7 +13408,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G169" s="4" t="n">
+      <c r="G169" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -13426,7 +13441,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N169" s="4" t="n">
+      <c r="N169" s="8" t="n">
         <v>70.964</v>
       </c>
       <c r="O169" s="4" t="inlineStr">
@@ -13472,7 +13487,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G170" s="4" t="n">
+      <c r="G170" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -13505,7 +13520,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N170" s="4" t="n">
+      <c r="N170" s="8" t="n">
         <v>71.172</v>
       </c>
       <c r="O170" s="4" t="inlineStr">
@@ -13551,7 +13566,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G171" s="4" t="n">
+      <c r="G171" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -13584,7 +13599,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N171" s="4" t="n">
+      <c r="N171" s="8" t="n">
         <v>71.17700000000001</v>
       </c>
       <c r="O171" s="4" t="inlineStr">
@@ -13630,7 +13645,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G172" s="4" t="n">
+      <c r="G172" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
@@ -13663,7 +13678,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N172" s="4" t="n">
+      <c r="N172" s="8" t="n">
         <v>71.38500000000001</v>
       </c>
       <c r="O172" s="4" t="inlineStr">
@@ -13709,7 +13724,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G173" s="4" t="n">
+      <c r="G173" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -13742,7 +13757,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N173" s="4" t="n">
+      <c r="N173" s="8" t="n">
         <v>71.283</v>
       </c>
       <c r="O173" s="4" t="inlineStr">
@@ -13788,7 +13803,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G174" s="4" t="n">
+      <c r="G174" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -13821,7 +13836,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N174" s="4" t="n">
+      <c r="N174" s="8" t="n">
         <v>71.714</v>
       </c>
       <c r="O174" s="4" t="inlineStr">
@@ -13867,7 +13882,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G175" s="4" t="n">
+      <c r="G175" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
@@ -13900,7 +13915,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N175" s="4" t="n">
+      <c r="N175" s="8" t="n">
         <v>71.92</v>
       </c>
       <c r="O175" s="4" t="inlineStr">
@@ -13946,7 +13961,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G176" s="4" t="n">
+      <c r="G176" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -13979,7 +13994,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N176" s="4" t="n">
+      <c r="N176" s="8" t="n">
         <v>72.56</v>
       </c>
       <c r="O176" s="4" t="inlineStr">
@@ -14025,7 +14040,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G177" s="4" t="n">
+      <c r="G177" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
@@ -14058,7 +14073,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N177" s="4" t="n">
+      <c r="N177" s="8" t="n">
         <v>72.446</v>
       </c>
       <c r="O177" s="4" t="inlineStr">
@@ -14104,7 +14119,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G178" s="4" t="n">
+      <c r="G178" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
@@ -14137,7 +14152,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N178" s="4" t="n">
+      <c r="N178" s="8" t="n">
         <v>72.08799999999999</v>
       </c>
       <c r="O178" s="4" t="inlineStr">
@@ -14183,7 +14198,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G179" s="4" t="n">
+      <c r="G179" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -14216,7 +14231,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N179" s="4" t="n">
+      <c r="N179" s="8" t="n">
         <v>72.38800000000001</v>
       </c>
       <c r="O179" s="4" t="inlineStr">
@@ -14262,7 +14277,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G180" s="4" t="n">
+      <c r="G180" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
@@ -14295,7 +14310,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N180" s="4" t="n">
+      <c r="N180" s="8" t="n">
         <v>71.01900000000001</v>
       </c>
       <c r="O180" s="4" t="inlineStr">
@@ -14341,7 +14356,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G181" s="4" t="n">
+      <c r="G181" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
@@ -14374,7 +14389,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N181" s="4" t="n">
+      <c r="N181" s="8" t="n">
         <v>72.82299999999999</v>
       </c>
       <c r="O181" s="4" t="inlineStr">
@@ -14420,7 +14435,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G182" s="4" t="n">
+      <c r="G182" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -14453,7 +14468,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N182" s="4" t="n">
+      <c r="N182" s="8" t="n">
         <v>72.056</v>
       </c>
       <c r="O182" s="4" t="inlineStr">
@@ -14499,7 +14514,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G183" s="4" t="n">
+      <c r="G183" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
@@ -14532,7 +14547,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N183" s="4" t="n">
+      <c r="N183" s="8" t="n">
         <v>72.752</v>
       </c>
       <c r="O183" s="4" t="inlineStr">
@@ -14578,7 +14593,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G184" s="4" t="n">
+      <c r="G184" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
@@ -14611,7 +14626,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N184" s="4" t="n">
+      <c r="N184" s="8" t="n">
         <v>73.075</v>
       </c>
       <c r="O184" s="4" t="inlineStr">
@@ -14657,7 +14672,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G185" s="4" t="n">
+      <c r="G185" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
@@ -14690,7 +14705,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N185" s="4" t="n">
+      <c r="N185" s="8" t="n">
         <v>72.97199999999999</v>
       </c>
       <c r="O185" s="4" t="inlineStr">
@@ -14736,7 +14751,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G186" s="4" t="n">
+      <c r="G186" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
@@ -14769,7 +14784,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N186" s="4" t="n">
+      <c r="N186" s="8" t="n">
         <v>73.348</v>
       </c>
       <c r="O186" s="4" t="inlineStr">
@@ -14815,7 +14830,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G187" s="4" t="n">
+      <c r="G187" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
@@ -14848,7 +14863,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N187" s="4" t="n">
+      <c r="N187" s="8" t="n">
         <v>72.578</v>
       </c>
       <c r="O187" s="4" t="inlineStr">
@@ -14894,7 +14909,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G188" s="4" t="n">
+      <c r="G188" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
@@ -14927,7 +14942,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N188" s="4" t="n">
+      <c r="N188" s="8" t="n">
         <v>72.785</v>
       </c>
       <c r="O188" s="4" t="inlineStr">
@@ -14973,7 +14988,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G189" s="4" t="n">
+      <c r="G189" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
@@ -15006,7 +15021,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N189" s="4" t="n">
+      <c r="N189" s="8" t="n">
         <v>73.092</v>
       </c>
       <c r="O189" s="4" t="inlineStr">
@@ -15052,7 +15067,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G190" s="4" t="n">
+      <c r="G190" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
@@ -15085,7 +15100,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N190" s="4" t="n">
+      <c r="N190" s="8" t="n">
         <v>73.09</v>
       </c>
       <c r="O190" s="4" t="inlineStr">
@@ -15131,7 +15146,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G191" s="4" t="n">
+      <c r="G191" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -15164,7 +15179,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N191" s="4" t="n">
+      <c r="N191" s="8" t="n">
         <v>73.086</v>
       </c>
       <c r="O191" s="4" t="inlineStr">
@@ -15210,7 +15225,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G192" s="4" t="n">
+      <c r="G192" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -15243,7 +15258,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N192" s="4" t="n">
+      <c r="N192" s="8" t="n">
         <v>73.07599999999999</v>
       </c>
       <c r="O192" s="4" t="inlineStr">
@@ -15289,7 +15304,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G193" s="4" t="n">
+      <c r="G193" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -15322,7 +15337,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N193" s="4" t="n">
+      <c r="N193" s="8" t="n">
         <v>72.837</v>
       </c>
       <c r="O193" s="4" t="inlineStr">
@@ -15368,7 +15383,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G194" s="4" t="n">
+      <c r="G194" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
@@ -15401,7 +15416,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N194" s="4" t="n">
+      <c r="N194" s="8" t="n">
         <v>73.004</v>
       </c>
       <c r="O194" s="4" t="inlineStr">
@@ -15447,7 +15462,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G195" s="4" t="n">
+      <c r="G195" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
@@ -15480,7 +15495,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N195" s="4" t="n">
+      <c r="N195" s="8" t="n">
         <v>72.002</v>
       </c>
       <c r="O195" s="4" t="inlineStr">
@@ -15526,7 +15541,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G196" s="4" t="n">
+      <c r="G196" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
@@ -15559,7 +15574,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N196" s="4" t="n">
+      <c r="N196" s="8" t="n">
         <v>71.90300000000001</v>
       </c>
       <c r="O196" s="4" t="inlineStr">
@@ -15605,7 +15620,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G197" s="4" t="n">
+      <c r="G197" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
@@ -15638,7 +15653,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N197" s="4" t="n">
+      <c r="N197" s="8" t="n">
         <v>72.64100000000001</v>
       </c>
       <c r="O197" s="4" t="inlineStr">
@@ -15684,7 +15699,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G198" s="4" t="n">
+      <c r="G198" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
@@ -15717,7 +15732,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N198" s="4" t="n">
+      <c r="N198" s="8" t="n">
         <v>72.76600000000001</v>
       </c>
       <c r="O198" s="4" t="inlineStr">
@@ -15763,7 +15778,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G199" s="4" t="n">
+      <c r="G199" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
@@ -15796,7 +15811,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N199" s="4" t="n">
+      <c r="N199" s="8" t="n">
         <v>72.369</v>
       </c>
       <c r="O199" s="4" t="inlineStr">
@@ -15842,7 +15857,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G200" s="4" t="n">
+      <c r="G200" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
@@ -15875,7 +15890,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N200" s="4" t="n">
+      <c r="N200" s="8" t="n">
         <v>71.536</v>
       </c>
       <c r="O200" s="4" t="inlineStr">
@@ -15921,7 +15936,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G201" s="4" t="n">
+      <c r="G201" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
@@ -15954,7 +15969,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N201" s="4" t="n">
+      <c r="N201" s="8" t="n">
         <v>72.566</v>
       </c>
       <c r="O201" s="4" t="inlineStr">
@@ -16000,7 +16015,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G202" s="4" t="n">
+      <c r="G202" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
@@ -16033,7 +16048,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N202" s="4" t="n">
+      <c r="N202" s="8" t="n">
         <v>72.514</v>
       </c>
       <c r="O202" s="4" t="inlineStr">
@@ -16079,7 +16094,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G203" s="4" t="n">
+      <c r="G203" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
@@ -16112,7 +16127,7 @@
           <t>Esperanza de vida al nacer</t>
         </is>
       </c>
-      <c r="N203" s="4" t="n">
+      <c r="N203" s="8" t="n">
         <v>72.673</v>
       </c>
       <c r="O203" s="4" t="inlineStr">
@@ -16158,7 +16173,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G204" s="4" t="n">
+      <c r="G204" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
@@ -16235,7 +16250,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G205" s="4" t="n">
+      <c r="G205" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
@@ -16268,7 +16283,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N205" s="4" t="n">
+      <c r="N205" s="8" t="n">
         <v>56.523</v>
       </c>
       <c r="O205" s="4" t="inlineStr">
@@ -16314,7 +16329,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G206" s="4" t="n">
+      <c r="G206" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
@@ -16347,7 +16362,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N206" s="4" t="n">
+      <c r="N206" s="8" t="n">
         <v>57.306</v>
       </c>
       <c r="O206" s="4" t="inlineStr">
@@ -16393,7 +16408,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G207" s="4" t="n">
+      <c r="G207" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
@@ -16426,7 +16441,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N207" s="4" t="n">
+      <c r="N207" s="8" t="n">
         <v>57.78</v>
       </c>
       <c r="O207" s="4" t="inlineStr">
@@ -16472,7 +16487,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G208" s="4" t="n">
+      <c r="G208" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
@@ -16505,7 +16520,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N208" s="4" t="n">
+      <c r="N208" s="8" t="n">
         <v>58.724</v>
       </c>
       <c r="O208" s="4" t="inlineStr">
@@ -16551,7 +16566,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G209" s="4" t="n">
+      <c r="G209" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
@@ -16584,7 +16599,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N209" s="4" t="n">
+      <c r="N209" s="8" t="n">
         <v>59.39</v>
       </c>
       <c r="O209" s="4" t="inlineStr">
@@ -16630,7 +16645,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G210" s="4" t="n">
+      <c r="G210" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
@@ -16663,7 +16678,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N210" s="4" t="n">
+      <c r="N210" s="8" t="n">
         <v>60.188</v>
       </c>
       <c r="O210" s="4" t="inlineStr">
@@ -16709,7 +16724,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G211" s="4" t="n">
+      <c r="G211" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
@@ -16742,7 +16757,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N211" s="4" t="n">
+      <c r="N211" s="8" t="n">
         <v>61.074</v>
       </c>
       <c r="O211" s="4" t="inlineStr">
@@ -16788,7 +16803,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G212" s="4" t="n">
+      <c r="G212" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
@@ -16821,7 +16836,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N212" s="4" t="n">
+      <c r="N212" s="8" t="n">
         <v>61.84</v>
       </c>
       <c r="O212" s="4" t="inlineStr">
@@ -16867,7 +16882,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G213" s="4" t="n">
+      <c r="G213" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
@@ -16900,7 +16915,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N213" s="4" t="n">
+      <c r="N213" s="8" t="n">
         <v>62.116</v>
       </c>
       <c r="O213" s="4" t="inlineStr">
@@ -16946,7 +16961,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G214" s="4" t="n">
+      <c r="G214" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
@@ -16979,7 +16994,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N214" s="4" t="n">
+      <c r="N214" s="8" t="n">
         <v>62.234</v>
       </c>
       <c r="O214" s="4" t="inlineStr">
@@ -17025,7 +17040,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G215" s="4" t="n">
+      <c r="G215" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
@@ -17058,7 +17073,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N215" s="4" t="n">
+      <c r="N215" s="8" t="n">
         <v>62.982</v>
       </c>
       <c r="O215" s="4" t="inlineStr">
@@ -17104,7 +17119,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G216" s="4" t="n">
+      <c r="G216" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
@@ -17137,7 +17152,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N216" s="4" t="n">
+      <c r="N216" s="8" t="n">
         <v>63.341</v>
       </c>
       <c r="O216" s="4" t="inlineStr">
@@ -17183,7 +17198,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G217" s="4" t="n">
+      <c r="G217" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
@@ -17216,7 +17231,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N217" s="4" t="n">
+      <c r="N217" s="8" t="n">
         <v>63.624</v>
       </c>
       <c r="O217" s="4" t="inlineStr">
@@ -17262,7 +17277,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G218" s="4" t="n">
+      <c r="G218" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
@@ -17295,7 +17310,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N218" s="4" t="n">
+      <c r="N218" s="8" t="n">
         <v>63.701</v>
       </c>
       <c r="O218" s="4" t="inlineStr">
@@ -17341,7 +17356,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G219" s="4" t="n">
+      <c r="G219" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
@@ -17374,7 +17389,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N219" s="4" t="n">
+      <c r="N219" s="8" t="n">
         <v>64.105</v>
       </c>
       <c r="O219" s="4" t="inlineStr">
@@ -17420,7 +17435,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G220" s="4" t="n">
+      <c r="G220" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
@@ -17453,7 +17468,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N220" s="4" t="n">
+      <c r="N220" s="8" t="n">
         <v>64.503</v>
       </c>
       <c r="O220" s="4" t="inlineStr">
@@ -17499,7 +17514,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G221" s="4" t="n">
+      <c r="G221" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
@@ -17532,7 +17547,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N221" s="4" t="n">
+      <c r="N221" s="8" t="n">
         <v>65.081</v>
       </c>
       <c r="O221" s="4" t="inlineStr">
@@ -17578,7 +17593,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G222" s="4" t="n">
+      <c r="G222" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
@@ -17611,7 +17626,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N222" s="4" t="n">
+      <c r="N222" s="8" t="n">
         <v>65.33499999999999</v>
       </c>
       <c r="O222" s="4" t="inlineStr">
@@ -17657,7 +17672,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G223" s="4" t="n">
+      <c r="G223" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
@@ -17690,7 +17705,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N223" s="4" t="n">
+      <c r="N223" s="8" t="n">
         <v>65.55</v>
       </c>
       <c r="O223" s="4" t="inlineStr">
@@ -17736,7 +17751,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G224" s="4" t="n">
+      <c r="G224" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
@@ -17769,7 +17784,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N224" s="4" t="n">
+      <c r="N224" s="8" t="n">
         <v>65.637</v>
       </c>
       <c r="O224" s="4" t="inlineStr">
@@ -17815,7 +17830,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G225" s="4" t="n">
+      <c r="G225" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
@@ -17848,7 +17863,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N225" s="4" t="n">
+      <c r="N225" s="8" t="n">
         <v>65.498</v>
       </c>
       <c r="O225" s="4" t="inlineStr">
@@ -17894,7 +17909,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G226" s="4" t="n">
+      <c r="G226" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
@@ -17927,7 +17942,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N226" s="4" t="n">
+      <c r="N226" s="8" t="n">
         <v>66.059</v>
       </c>
       <c r="O226" s="4" t="inlineStr">
@@ -17973,7 +17988,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G227" s="4" t="n">
+      <c r="G227" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
@@ -18006,7 +18021,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N227" s="4" t="n">
+      <c r="N227" s="8" t="n">
         <v>66.277</v>
       </c>
       <c r="O227" s="4" t="inlineStr">
@@ -18052,7 +18067,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G228" s="4" t="n">
+      <c r="G228" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
@@ -18085,7 +18100,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N228" s="4" t="n">
+      <c r="N228" s="8" t="n">
         <v>66.89</v>
       </c>
       <c r="O228" s="4" t="inlineStr">
@@ -18131,7 +18146,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G229" s="4" t="n">
+      <c r="G229" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
@@ -18164,7 +18179,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N229" s="4" t="n">
+      <c r="N229" s="8" t="n">
         <v>67.139</v>
       </c>
       <c r="O229" s="4" t="inlineStr">
@@ -18210,7 +18225,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G230" s="4" t="n">
+      <c r="G230" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
@@ -18243,7 +18258,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N230" s="4" t="n">
+      <c r="N230" s="8" t="n">
         <v>67.499</v>
       </c>
       <c r="O230" s="4" t="inlineStr">
@@ -18289,7 +18304,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G231" s="4" t="n">
+      <c r="G231" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
@@ -18322,7 +18337,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N231" s="4" t="n">
+      <c r="N231" s="8" t="n">
         <v>68.06399999999999</v>
       </c>
       <c r="O231" s="4" t="inlineStr">
@@ -18368,7 +18383,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G232" s="4" t="n">
+      <c r="G232" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
@@ -18401,7 +18416,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N232" s="4" t="n">
+      <c r="N232" s="8" t="n">
         <v>68.12</v>
       </c>
       <c r="O232" s="4" t="inlineStr">
@@ -18447,7 +18462,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G233" s="4" t="n">
+      <c r="G233" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
@@ -18480,7 +18495,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N233" s="4" t="n">
+      <c r="N233" s="8" t="n">
         <v>68.125</v>
       </c>
       <c r="O233" s="4" t="inlineStr">
@@ -18526,7 +18541,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G234" s="4" t="n">
+      <c r="G234" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
@@ -18559,7 +18574,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N234" s="4" t="n">
+      <c r="N234" s="8" t="n">
         <v>68.009</v>
       </c>
       <c r="O234" s="4" t="inlineStr">
@@ -18605,7 +18620,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G235" s="4" t="n">
+      <c r="G235" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
@@ -18638,7 +18653,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N235" s="4" t="n">
+      <c r="N235" s="8" t="n">
         <v>68.364</v>
       </c>
       <c r="O235" s="4" t="inlineStr">
@@ -18684,7 +18699,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G236" s="4" t="n">
+      <c r="G236" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
@@ -18717,7 +18732,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N236" s="4" t="n">
+      <c r="N236" s="8" t="n">
         <v>68.286</v>
       </c>
       <c r="O236" s="4" t="inlineStr">
@@ -18763,7 +18778,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G237" s="4" t="n">
+      <c r="G237" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
@@ -18796,7 +18811,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N237" s="4" t="n">
+      <c r="N237" s="8" t="n">
         <v>68.13200000000001</v>
       </c>
       <c r="O237" s="4" t="inlineStr">
@@ -18842,7 +18857,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G238" s="4" t="n">
+      <c r="G238" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
@@ -18875,7 +18890,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N238" s="4" t="n">
+      <c r="N238" s="8" t="n">
         <v>68.2</v>
       </c>
       <c r="O238" s="4" t="inlineStr">
@@ -18921,7 +18936,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G239" s="4" t="n">
+      <c r="G239" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
@@ -18954,7 +18969,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N239" s="4" t="n">
+      <c r="N239" s="8" t="n">
         <v>68.114</v>
       </c>
       <c r="O239" s="4" t="inlineStr">
@@ -19000,7 +19015,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G240" s="4" t="n">
+      <c r="G240" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
@@ -19033,7 +19048,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N240" s="4" t="n">
+      <c r="N240" s="8" t="n">
         <v>68.655</v>
       </c>
       <c r="O240" s="4" t="inlineStr">
@@ -19079,7 +19094,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G241" s="4" t="n">
+      <c r="G241" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
@@ -19112,7 +19127,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N241" s="4" t="n">
+      <c r="N241" s="8" t="n">
         <v>68.896</v>
       </c>
       <c r="O241" s="4" t="inlineStr">
@@ -19158,7 +19173,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G242" s="4" t="n">
+      <c r="G242" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
@@ -19191,7 +19206,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N242" s="4" t="n">
+      <c r="N242" s="8" t="n">
         <v>69.583</v>
       </c>
       <c r="O242" s="4" t="inlineStr">
@@ -19237,7 +19252,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G243" s="4" t="n">
+      <c r="G243" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
@@ -19270,7 +19285,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N243" s="4" t="n">
+      <c r="N243" s="8" t="n">
         <v>69.252</v>
       </c>
       <c r="O243" s="4" t="inlineStr">
@@ -19316,7 +19331,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G244" s="4" t="n">
+      <c r="G244" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
@@ -19349,7 +19364,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N244" s="4" t="n">
+      <c r="N244" s="8" t="n">
         <v>68.889</v>
       </c>
       <c r="O244" s="4" t="inlineStr">
@@ -19395,7 +19410,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G245" s="4" t="n">
+      <c r="G245" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
@@ -19428,7 +19443,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N245" s="4" t="n">
+      <c r="N245" s="8" t="n">
         <v>68.75700000000001</v>
       </c>
       <c r="O245" s="4" t="inlineStr">
@@ -19474,7 +19489,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G246" s="4" t="n">
+      <c r="G246" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
@@ -19507,7 +19522,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N246" s="4" t="n">
+      <c r="N246" s="8" t="n">
         <v>67.01900000000001</v>
       </c>
       <c r="O246" s="4" t="inlineStr">
@@ -19553,7 +19568,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G247" s="4" t="n">
+      <c r="G247" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
@@ -19586,7 +19601,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N247" s="4" t="n">
+      <c r="N247" s="8" t="n">
         <v>69.015</v>
       </c>
       <c r="O247" s="4" t="inlineStr">
@@ -19632,7 +19647,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G248" s="4" t="n">
+      <c r="G248" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
@@ -19665,7 +19680,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N248" s="4" t="n">
+      <c r="N248" s="8" t="n">
         <v>68.2</v>
       </c>
       <c r="O248" s="4" t="inlineStr">
@@ -19711,7 +19726,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G249" s="4" t="n">
+      <c r="G249" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
@@ -19744,7 +19759,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N249" s="4" t="n">
+      <c r="N249" s="8" t="n">
         <v>69.014</v>
       </c>
       <c r="O249" s="4" t="inlineStr">
@@ -19790,7 +19805,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G250" s="4" t="n">
+      <c r="G250" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
@@ -19823,7 +19838,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N250" s="4" t="n">
+      <c r="N250" s="8" t="n">
         <v>69.378</v>
       </c>
       <c r="O250" s="4" t="inlineStr">
@@ -19869,7 +19884,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G251" s="4" t="n">
+      <c r="G251" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
@@ -19902,7 +19917,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N251" s="4" t="n">
+      <c r="N251" s="8" t="n">
         <v>69.006</v>
       </c>
       <c r="O251" s="4" t="inlineStr">
@@ -19948,7 +19963,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G252" s="4" t="n">
+      <c r="G252" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
@@ -19981,7 +19996,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N252" s="4" t="n">
+      <c r="N252" s="8" t="n">
         <v>69.283</v>
       </c>
       <c r="O252" s="4" t="inlineStr">
@@ -20027,7 +20042,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G253" s="4" t="n">
+      <c r="G253" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
@@ -20060,7 +20075,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N253" s="4" t="n">
+      <c r="N253" s="8" t="n">
         <v>68.26600000000001</v>
       </c>
       <c r="O253" s="4" t="inlineStr">
@@ -20106,7 +20121,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G254" s="4" t="n">
+      <c r="G254" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
@@ -20139,7 +20154,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N254" s="4" t="n">
+      <c r="N254" s="8" t="n">
         <v>68.54600000000001</v>
       </c>
       <c r="O254" s="4" t="inlineStr">
@@ -20185,7 +20200,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G255" s="4" t="n">
+      <c r="G255" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
@@ -20218,7 +20233,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N255" s="4" t="n">
+      <c r="N255" s="8" t="n">
         <v>69.06399999999999</v>
       </c>
       <c r="O255" s="4" t="inlineStr">
@@ -20264,7 +20279,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G256" s="4" t="n">
+      <c r="G256" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
@@ -20297,7 +20312,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N256" s="4" t="n">
+      <c r="N256" s="8" t="n">
         <v>68.714</v>
       </c>
       <c r="O256" s="4" t="inlineStr">
@@ -20343,7 +20358,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G257" s="4" t="n">
+      <c r="G257" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
@@ -20376,7 +20391,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N257" s="4" t="n">
+      <c r="N257" s="8" t="n">
         <v>68.82899999999999</v>
       </c>
       <c r="O257" s="4" t="inlineStr">
@@ -20422,7 +20437,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G258" s="4" t="n">
+      <c r="G258" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
@@ -20455,7 +20470,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N258" s="4" t="n">
+      <c r="N258" s="8" t="n">
         <v>68.94</v>
       </c>
       <c r="O258" s="4" t="inlineStr">
@@ -20501,7 +20516,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G259" s="4" t="n">
+      <c r="G259" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
@@ -20534,7 +20549,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N259" s="4" t="n">
+      <c r="N259" s="8" t="n">
         <v>68.61799999999999</v>
       </c>
       <c r="O259" s="4" t="inlineStr">
@@ -20580,7 +20595,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G260" s="4" t="n">
+      <c r="G260" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
@@ -20613,7 +20628,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N260" s="4" t="n">
+      <c r="N260" s="8" t="n">
         <v>68.871</v>
       </c>
       <c r="O260" s="4" t="inlineStr">
@@ -20659,7 +20674,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G261" s="4" t="n">
+      <c r="G261" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
@@ -20692,7 +20707,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N261" s="4" t="n">
+      <c r="N261" s="8" t="n">
         <v>67.563</v>
       </c>
       <c r="O261" s="4" t="inlineStr">
@@ -20738,7 +20753,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G262" s="4" t="n">
+      <c r="G262" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
@@ -20771,7 +20786,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N262" s="4" t="n">
+      <c r="N262" s="8" t="n">
         <v>67.776</v>
       </c>
       <c r="O262" s="4" t="inlineStr">
@@ -20817,7 +20832,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G263" s="4" t="n">
+      <c r="G263" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
@@ -20850,7 +20865,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N263" s="4" t="n">
+      <c r="N263" s="8" t="n">
         <v>68.902</v>
       </c>
       <c r="O263" s="4" t="inlineStr">
@@ -20896,7 +20911,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G264" s="4" t="n">
+      <c r="G264" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
@@ -20929,7 +20944,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N264" s="4" t="n">
+      <c r="N264" s="8" t="n">
         <v>69.02500000000001</v>
       </c>
       <c r="O264" s="4" t="inlineStr">
@@ -20975,7 +20990,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G265" s="4" t="n">
+      <c r="G265" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
@@ -21008,7 +21023,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N265" s="4" t="n">
+      <c r="N265" s="8" t="n">
         <v>68.459</v>
       </c>
       <c r="O265" s="4" t="inlineStr">
@@ -21054,7 +21069,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G266" s="4" t="n">
+      <c r="G266" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
@@ -21087,7 +21102,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N266" s="4" t="n">
+      <c r="N266" s="8" t="n">
         <v>67.68300000000001</v>
       </c>
       <c r="O266" s="4" t="inlineStr">
@@ -21133,7 +21148,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G267" s="4" t="n">
+      <c r="G267" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
@@ -21166,7 +21181,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N267" s="4" t="n">
+      <c r="N267" s="8" t="n">
         <v>68.789</v>
       </c>
       <c r="O267" s="4" t="inlineStr">
@@ -21212,7 +21227,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G268" s="4" t="n">
+      <c r="G268" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
@@ -21245,7 +21260,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N268" s="4" t="n">
+      <c r="N268" s="8" t="n">
         <v>68.72</v>
       </c>
       <c r="O268" s="4" t="inlineStr">
@@ -21291,7 +21306,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G269" s="4" t="n">
+      <c r="G269" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
@@ -21324,7 +21339,7 @@
           <t>Esperanza de vida masculina</t>
         </is>
       </c>
-      <c r="N269" s="4" t="n">
+      <c r="N269" s="8" t="n">
         <v>68.88500000000001</v>
       </c>
       <c r="O269" s="4" t="inlineStr">
@@ -21370,7 +21385,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G270" s="4" t="n">
+      <c r="G270" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
@@ -21447,7 +21462,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G271" s="4" t="n">
+      <c r="G271" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
@@ -21480,7 +21495,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N271" s="4" t="n">
+      <c r="N271" s="8" t="n">
         <v>6.382</v>
       </c>
       <c r="O271" s="4" t="inlineStr">
@@ -21526,7 +21541,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G272" s="4" t="n">
+      <c r="G272" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
@@ -21559,7 +21574,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N272" s="4" t="n">
+      <c r="N272" s="8" t="n">
         <v>6.298</v>
       </c>
       <c r="O272" s="4" t="inlineStr">
@@ -21605,7 +21620,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G273" s="4" t="n">
+      <c r="G273" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
@@ -21638,7 +21653,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N273" s="4" t="n">
+      <c r="N273" s="8" t="n">
         <v>6.231</v>
       </c>
       <c r="O273" s="4" t="inlineStr">
@@ -21684,7 +21699,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G274" s="4" t="n">
+      <c r="G274" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
@@ -21717,7 +21732,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N274" s="4" t="n">
+      <c r="N274" s="8" t="n">
         <v>6.155</v>
       </c>
       <c r="O274" s="4" t="inlineStr">
@@ -21763,7 +21778,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G275" s="4" t="n">
+      <c r="G275" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
@@ -21796,7 +21811,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N275" s="4" t="n">
+      <c r="N275" s="8" t="n">
         <v>6.071</v>
       </c>
       <c r="O275" s="4" t="inlineStr">
@@ -21842,7 +21857,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G276" s="4" t="n">
+      <c r="G276" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
@@ -21875,7 +21890,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N276" s="4" t="n">
+      <c r="N276" s="8" t="n">
         <v>5.977</v>
       </c>
       <c r="O276" s="4" t="inlineStr">
@@ -21921,7 +21936,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G277" s="4" t="n">
+      <c r="G277" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
@@ -21954,7 +21969,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N277" s="4" t="n">
+      <c r="N277" s="8" t="n">
         <v>5.87</v>
       </c>
       <c r="O277" s="4" t="inlineStr">
@@ -22000,7 +22015,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G278" s="4" t="n">
+      <c r="G278" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
@@ -22033,7 +22048,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N278" s="4" t="n">
+      <c r="N278" s="8" t="n">
         <v>5.748</v>
       </c>
       <c r="O278" s="4" t="inlineStr">
@@ -22079,7 +22094,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G279" s="4" t="n">
+      <c r="G279" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
@@ -22112,7 +22127,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N279" s="4" t="n">
+      <c r="N279" s="8" t="n">
         <v>5.614</v>
       </c>
       <c r="O279" s="4" t="inlineStr">
@@ -22158,7 +22173,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G280" s="4" t="n">
+      <c r="G280" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
@@ -22191,7 +22206,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N280" s="4" t="n">
+      <c r="N280" s="8" t="n">
         <v>5.469</v>
       </c>
       <c r="O280" s="4" t="inlineStr">
@@ -22237,7 +22252,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G281" s="4" t="n">
+      <c r="G281" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
@@ -22270,7 +22285,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N281" s="4" t="n">
+      <c r="N281" s="8" t="n">
         <v>5.321</v>
       </c>
       <c r="O281" s="4" t="inlineStr">
@@ -22316,7 +22331,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G282" s="4" t="n">
+      <c r="G282" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
@@ -22349,7 +22364,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N282" s="4" t="n">
+      <c r="N282" s="8" t="n">
         <v>5.174</v>
       </c>
       <c r="O282" s="4" t="inlineStr">
@@ -22395,7 +22410,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G283" s="4" t="n">
+      <c r="G283" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
@@ -22428,7 +22443,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N283" s="4" t="n">
+      <c r="N283" s="8" t="n">
         <v>5.035</v>
       </c>
       <c r="O283" s="4" t="inlineStr">
@@ -22474,7 +22489,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G284" s="4" t="n">
+      <c r="G284" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
@@ -22507,7 +22522,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N284" s="4" t="n">
+      <c r="N284" s="8" t="n">
         <v>4.906</v>
       </c>
       <c r="O284" s="4" t="inlineStr">
@@ -22553,7 +22568,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G285" s="4" t="n">
+      <c r="G285" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
@@ -22586,7 +22601,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N285" s="4" t="n">
+      <c r="N285" s="8" t="n">
         <v>4.791</v>
       </c>
       <c r="O285" s="4" t="inlineStr">
@@ -22632,7 +22647,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G286" s="4" t="n">
+      <c r="G286" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
@@ -22665,7 +22680,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N286" s="4" t="n">
+      <c r="N286" s="8" t="n">
         <v>4.686</v>
       </c>
       <c r="O286" s="4" t="inlineStr">
@@ -22711,7 +22726,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G287" s="4" t="n">
+      <c r="G287" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
@@ -22744,7 +22759,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N287" s="4" t="n">
+      <c r="N287" s="8" t="n">
         <v>4.589</v>
       </c>
       <c r="O287" s="4" t="inlineStr">
@@ -22790,7 +22805,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G288" s="4" t="n">
+      <c r="G288" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
@@ -22823,7 +22838,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N288" s="4" t="n">
+      <c r="N288" s="8" t="n">
         <v>4.494</v>
       </c>
       <c r="O288" s="4" t="inlineStr">
@@ -22869,7 +22884,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G289" s="4" t="n">
+      <c r="G289" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
@@ -22902,7 +22917,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N289" s="4" t="n">
+      <c r="N289" s="8" t="n">
         <v>4.397</v>
       </c>
       <c r="O289" s="4" t="inlineStr">
@@ -22948,7 +22963,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G290" s="4" t="n">
+      <c r="G290" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
@@ -22981,7 +22996,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N290" s="4" t="n">
+      <c r="N290" s="8" t="n">
         <v>4.298</v>
       </c>
       <c r="O290" s="4" t="inlineStr">
@@ -23027,7 +23042,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G291" s="4" t="n">
+      <c r="G291" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
@@ -23060,7 +23075,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N291" s="4" t="n">
+      <c r="N291" s="8" t="n">
         <v>4.2</v>
       </c>
       <c r="O291" s="4" t="inlineStr">
@@ -23106,7 +23121,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G292" s="4" t="n">
+      <c r="G292" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
@@ -23139,7 +23154,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N292" s="4" t="n">
+      <c r="N292" s="8" t="n">
         <v>4.104</v>
       </c>
       <c r="O292" s="4" t="inlineStr">
@@ -23185,7 +23200,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G293" s="4" t="n">
+      <c r="G293" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
@@ -23218,7 +23233,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N293" s="4" t="n">
+      <c r="N293" s="8" t="n">
         <v>4.014</v>
       </c>
       <c r="O293" s="4" t="inlineStr">
@@ -23264,7 +23279,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G294" s="4" t="n">
+      <c r="G294" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
@@ -23297,7 +23312,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N294" s="4" t="n">
+      <c r="N294" s="8" t="n">
         <v>3.933</v>
       </c>
       <c r="O294" s="4" t="inlineStr">
@@ -23343,7 +23358,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G295" s="4" t="n">
+      <c r="G295" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
@@ -23376,7 +23391,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N295" s="4" t="n">
+      <c r="N295" s="8" t="n">
         <v>3.861</v>
       </c>
       <c r="O295" s="4" t="inlineStr">
@@ -23422,7 +23437,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G296" s="4" t="n">
+      <c r="G296" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
@@ -23455,7 +23470,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N296" s="4" t="n">
+      <c r="N296" s="8" t="n">
         <v>3.794</v>
       </c>
       <c r="O296" s="4" t="inlineStr">
@@ -23501,7 +23516,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G297" s="4" t="n">
+      <c r="G297" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
@@ -23534,7 +23549,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N297" s="4" t="n">
+      <c r="N297" s="8" t="n">
         <v>3.73</v>
       </c>
       <c r="O297" s="4" t="inlineStr">
@@ -23580,7 +23595,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G298" s="4" t="n">
+      <c r="G298" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
@@ -23613,7 +23628,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N298" s="4" t="n">
+      <c r="N298" s="8" t="n">
         <v>3.665</v>
       </c>
       <c r="O298" s="4" t="inlineStr">
@@ -23659,7 +23674,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G299" s="4" t="n">
+      <c r="G299" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
@@ -23692,7 +23707,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N299" s="4" t="n">
+      <c r="N299" s="8" t="n">
         <v>3.597</v>
       </c>
       <c r="O299" s="4" t="inlineStr">
@@ -23738,7 +23753,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G300" s="4" t="n">
+      <c r="G300" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
@@ -23771,7 +23786,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N300" s="4" t="n">
+      <c r="N300" s="8" t="n">
         <v>3.524</v>
       </c>
       <c r="O300" s="4" t="inlineStr">
@@ -23817,7 +23832,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G301" s="4" t="n">
+      <c r="G301" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
@@ -23850,7 +23865,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N301" s="4" t="n">
+      <c r="N301" s="8" t="n">
         <v>3.448</v>
       </c>
       <c r="O301" s="4" t="inlineStr">
@@ -23896,7 +23911,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G302" s="4" t="n">
+      <c r="G302" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
@@ -23929,7 +23944,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N302" s="4" t="n">
+      <c r="N302" s="8" t="n">
         <v>3.37</v>
       </c>
       <c r="O302" s="4" t="inlineStr">
@@ -23975,7 +23990,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G303" s="4" t="n">
+      <c r="G303" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
@@ -24008,7 +24023,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N303" s="4" t="n">
+      <c r="N303" s="8" t="n">
         <v>3.292</v>
       </c>
       <c r="O303" s="4" t="inlineStr">
@@ -24054,7 +24069,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G304" s="4" t="n">
+      <c r="G304" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
@@ -24087,7 +24102,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N304" s="4" t="n">
+      <c r="N304" s="8" t="n">
         <v>3.218</v>
       </c>
       <c r="O304" s="4" t="inlineStr">
@@ -24133,7 +24148,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G305" s="4" t="n">
+      <c r="G305" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
@@ -24166,7 +24181,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N305" s="4" t="n">
+      <c r="N305" s="8" t="n">
         <v>3.147</v>
       </c>
       <c r="O305" s="4" t="inlineStr">
@@ -24212,7 +24227,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G306" s="4" t="n">
+      <c r="G306" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
@@ -24245,7 +24260,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N306" s="4" t="n">
+      <c r="N306" s="8" t="n">
         <v>3.082</v>
       </c>
       <c r="O306" s="4" t="inlineStr">
@@ -24291,7 +24306,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G307" s="4" t="n">
+      <c r="G307" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
@@ -24324,7 +24339,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N307" s="4" t="n">
+      <c r="N307" s="8" t="n">
         <v>3.022</v>
       </c>
       <c r="O307" s="4" t="inlineStr">
@@ -24370,7 +24385,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G308" s="4" t="n">
+      <c r="G308" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
@@ -24403,7 +24418,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N308" s="4" t="n">
+      <c r="N308" s="8" t="n">
         <v>2.967</v>
       </c>
       <c r="O308" s="4" t="inlineStr">
@@ -24449,7 +24464,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G309" s="4" t="n">
+      <c r="G309" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
@@ -24482,7 +24497,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N309" s="4" t="n">
+      <c r="N309" s="8" t="n">
         <v>2.912</v>
       </c>
       <c r="O309" s="4" t="inlineStr">
@@ -24528,7 +24543,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G310" s="4" t="n">
+      <c r="G310" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
@@ -24561,7 +24576,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N310" s="4" t="n">
+      <c r="N310" s="8" t="n">
         <v>2.856</v>
       </c>
       <c r="O310" s="4" t="inlineStr">
@@ -24607,7 +24622,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G311" s="4" t="n">
+      <c r="G311" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
@@ -24640,7 +24655,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N311" s="4" t="n">
+      <c r="N311" s="8" t="n">
         <v>2.79</v>
       </c>
       <c r="O311" s="4" t="inlineStr">
@@ -24686,7 +24701,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G312" s="4" t="n">
+      <c r="G312" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
@@ -24719,7 +24734,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N312" s="4" t="n">
+      <c r="N312" s="8" t="n">
         <v>2.779</v>
       </c>
       <c r="O312" s="4" t="inlineStr">
@@ -24765,7 +24780,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G313" s="4" t="n">
+      <c r="G313" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
@@ -24798,7 +24813,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N313" s="4" t="n">
+      <c r="N313" s="8" t="n">
         <v>2.739</v>
       </c>
       <c r="O313" s="4" t="inlineStr">
@@ -24844,7 +24859,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G314" s="4" t="n">
+      <c r="G314" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
@@ -24877,7 +24892,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N314" s="4" t="n">
+      <c r="N314" s="8" t="n">
         <v>2.703</v>
       </c>
       <c r="O314" s="4" t="inlineStr">
@@ -24923,7 +24938,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G315" s="4" t="n">
+      <c r="G315" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
@@ -24956,7 +24971,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N315" s="4" t="n">
+      <c r="N315" s="8" t="n">
         <v>2.639</v>
       </c>
       <c r="O315" s="4" t="inlineStr">
@@ -25002,7 +25017,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G316" s="4" t="n">
+      <c r="G316" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
@@ -25035,7 +25050,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N316" s="4" t="n">
+      <c r="N316" s="8" t="n">
         <v>2.629</v>
       </c>
       <c r="O316" s="4" t="inlineStr">
@@ -25081,7 +25096,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G317" s="4" t="n">
+      <c r="G317" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
@@ -25114,7 +25129,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N317" s="4" t="n">
+      <c r="N317" s="8" t="n">
         <v>2.595</v>
       </c>
       <c r="O317" s="4" t="inlineStr">
@@ -25160,7 +25175,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G318" s="4" t="n">
+      <c r="G318" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
@@ -25193,7 +25208,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N318" s="4" t="n">
+      <c r="N318" s="8" t="n">
         <v>2.524</v>
       </c>
       <c r="O318" s="4" t="inlineStr">
@@ -25239,7 +25254,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G319" s="4" t="n">
+      <c r="G319" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
@@ -25272,7 +25287,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N319" s="4" t="n">
+      <c r="N319" s="8" t="n">
         <v>2.475</v>
       </c>
       <c r="O319" s="4" t="inlineStr">
@@ -25318,7 +25333,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G320" s="4" t="n">
+      <c r="G320" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
@@ -25351,7 +25366,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N320" s="4" t="n">
+      <c r="N320" s="8" t="n">
         <v>2.422</v>
       </c>
       <c r="O320" s="4" t="inlineStr">
@@ -25397,7 +25412,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G321" s="4" t="n">
+      <c r="G321" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
@@ -25430,7 +25445,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N321" s="4" t="n">
+      <c r="N321" s="8" t="n">
         <v>2.396</v>
       </c>
       <c r="O321" s="4" t="inlineStr">
@@ -25476,7 +25491,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G322" s="4" t="n">
+      <c r="G322" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
@@ -25509,7 +25524,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N322" s="4" t="n">
+      <c r="N322" s="8" t="n">
         <v>2.398</v>
       </c>
       <c r="O322" s="4" t="inlineStr">
@@ -25555,7 +25570,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G323" s="4" t="n">
+      <c r="G323" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
@@ -25588,7 +25603,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N323" s="4" t="n">
+      <c r="N323" s="8" t="n">
         <v>2.379</v>
       </c>
       <c r="O323" s="4" t="inlineStr">
@@ -25634,7 +25649,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G324" s="4" t="n">
+      <c r="G324" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
@@ -25667,7 +25682,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N324" s="4" t="n">
+      <c r="N324" s="8" t="n">
         <v>2.334</v>
       </c>
       <c r="O324" s="4" t="inlineStr">
@@ -25713,7 +25728,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G325" s="4" t="n">
+      <c r="G325" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
@@ -25746,7 +25761,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N325" s="4" t="n">
+      <c r="N325" s="8" t="n">
         <v>2.296</v>
       </c>
       <c r="O325" s="4" t="inlineStr">
@@ -25792,7 +25807,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G326" s="4" t="n">
+      <c r="G326" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
@@ -25825,7 +25840,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N326" s="4" t="n">
+      <c r="N326" s="8" t="n">
         <v>2.253</v>
       </c>
       <c r="O326" s="4" t="inlineStr">
@@ -25871,7 +25886,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G327" s="4" t="n">
+      <c r="G327" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
@@ -25904,7 +25919,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N327" s="4" t="n">
+      <c r="N327" s="8" t="n">
         <v>2.217</v>
       </c>
       <c r="O327" s="4" t="inlineStr">
@@ -25950,7 +25965,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G328" s="4" t="n">
+      <c r="G328" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
@@ -25983,7 +25998,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N328" s="4" t="n">
+      <c r="N328" s="8" t="n">
         <v>2.183</v>
       </c>
       <c r="O328" s="4" t="inlineStr">
@@ -26029,7 +26044,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G329" s="4" t="n">
+      <c r="G329" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
@@ -26062,7 +26077,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N329" s="4" t="n">
+      <c r="N329" s="8" t="n">
         <v>2.151</v>
       </c>
       <c r="O329" s="4" t="inlineStr">
@@ -26108,7 +26123,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G330" s="4" t="n">
+      <c r="G330" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
@@ -26141,7 +26156,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N330" s="4" t="n">
+      <c r="N330" s="8" t="n">
         <v>2.131</v>
       </c>
       <c r="O330" s="4" t="inlineStr">
@@ -26187,7 +26202,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G331" s="4" t="n">
+      <c r="G331" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
@@ -26220,7 +26235,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N331" s="4" t="n">
+      <c r="N331" s="8" t="n">
         <v>2.116</v>
       </c>
       <c r="O331" s="4" t="inlineStr">
@@ -26266,7 +26281,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G332" s="4" t="n">
+      <c r="G332" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
@@ -26299,7 +26314,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N332" s="4" t="n">
+      <c r="N332" s="8" t="n">
         <v>2.105</v>
       </c>
       <c r="O332" s="4" t="inlineStr">
@@ -26345,7 +26360,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G333" s="4" t="n">
+      <c r="G333" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
@@ -26378,7 +26393,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N333" s="4" t="n">
+      <c r="N333" s="8" t="n">
         <v>2.088</v>
       </c>
       <c r="O333" s="4" t="inlineStr">
@@ -26424,7 +26439,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G334" s="4" t="n">
+      <c r="G334" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
@@ -26457,7 +26472,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N334" s="4" t="n">
+      <c r="N334" s="8" t="n">
         <v>2.079</v>
       </c>
       <c r="O334" s="4" t="inlineStr">
@@ -26503,7 +26518,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G335" s="4" t="n">
+      <c r="G335" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
@@ -26536,7 +26551,7 @@
           <t>Tasa de fertilidad</t>
         </is>
       </c>
-      <c r="N335" s="4" t="n">
+      <c r="N335" s="8" t="n">
         <v>2.077</v>
       </c>
       <c r="O335" s="4" t="inlineStr">
@@ -26582,7 +26597,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G336" s="4" t="n">
+      <c r="G336" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
@@ -26659,7 +26674,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G337" s="4" t="n">
+      <c r="G337" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H337" s="4" t="inlineStr">
@@ -26736,7 +26751,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G338" s="4" t="n">
+      <c r="G338" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H338" s="4" t="inlineStr">
@@ -26769,7 +26784,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N338" s="4" t="n">
+      <c r="N338" s="8" t="n">
         <v>3.5610998156399</v>
       </c>
       <c r="O338" s="4" t="inlineStr">
@@ -26815,7 +26830,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G339" s="4" t="n">
+      <c r="G339" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H339" s="4" t="inlineStr">
@@ -26848,7 +26863,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N339" s="4" t="n">
+      <c r="N339" s="8" t="n">
         <v>3.49723386798958</v>
       </c>
       <c r="O339" s="4" t="inlineStr">
@@ -26894,7 +26909,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G340" s="4" t="n">
+      <c r="G340" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H340" s="4" t="inlineStr">
@@ -26927,7 +26942,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N340" s="4" t="n">
+      <c r="N340" s="8" t="n">
         <v>3.44743054176691</v>
       </c>
       <c r="O340" s="4" t="inlineStr">
@@ -26973,7 +26988,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G341" s="4" t="n">
+      <c r="G341" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H341" s="4" t="inlineStr">
@@ -27006,7 +27021,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N341" s="4" t="n">
+      <c r="N341" s="8" t="n">
         <v>3.40229694421621</v>
       </c>
       <c r="O341" s="4" t="inlineStr">
@@ -27052,7 +27067,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G342" s="4" t="n">
+      <c r="G342" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H342" s="4" t="inlineStr">
@@ -27085,7 +27100,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N342" s="4" t="n">
+      <c r="N342" s="8" t="n">
         <v>3.35622144763596</v>
       </c>
       <c r="O342" s="4" t="inlineStr">
@@ -27131,7 +27146,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G343" s="4" t="n">
+      <c r="G343" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H343" s="4" t="inlineStr">
@@ -27164,7 +27179,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N343" s="4" t="n">
+      <c r="N343" s="8" t="n">
         <v>3.31693849961177</v>
       </c>
       <c r="O343" s="4" t="inlineStr">
@@ -27210,7 +27225,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G344" s="4" t="n">
+      <c r="G344" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H344" s="4" t="inlineStr">
@@ -27243,7 +27258,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N344" s="4" t="n">
+      <c r="N344" s="8" t="n">
         <v>3.27412842154232</v>
       </c>
       <c r="O344" s="4" t="inlineStr">
@@ -27289,7 +27304,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G345" s="4" t="n">
+      <c r="G345" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H345" s="4" t="inlineStr">
@@ -27322,7 +27337,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N345" s="4" t="n">
+      <c r="N345" s="8" t="n">
         <v>3.2204179987469</v>
       </c>
       <c r="O345" s="4" t="inlineStr">
@@ -27368,7 +27383,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G346" s="4" t="n">
+      <c r="G346" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H346" s="4" t="inlineStr">
@@ -27401,7 +27416,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N346" s="4" t="n">
+      <c r="N346" s="8" t="n">
         <v>3.15375291477192</v>
       </c>
       <c r="O346" s="4" t="inlineStr">
@@ -27447,7 +27462,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G347" s="4" t="n">
+      <c r="G347" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H347" s="4" t="inlineStr">
@@ -27480,7 +27495,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N347" s="4" t="n">
+      <c r="N347" s="8" t="n">
         <v>3.09913259359461</v>
       </c>
       <c r="O347" s="4" t="inlineStr">
@@ -27526,7 +27541,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G348" s="4" t="n">
+      <c r="G348" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H348" s="4" t="inlineStr">
@@ -27559,7 +27574,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N348" s="4" t="n">
+      <c r="N348" s="8" t="n">
         <v>3.05459422386915</v>
       </c>
       <c r="O348" s="4" t="inlineStr">
@@ -27605,7 +27620,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G349" s="4" t="n">
+      <c r="G349" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H349" s="4" t="inlineStr">
@@ -27638,7 +27653,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N349" s="4" t="n">
+      <c r="N349" s="8" t="n">
         <v>3.00500106904498</v>
       </c>
       <c r="O349" s="4" t="inlineStr">
@@ -27684,7 +27699,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G350" s="4" t="n">
+      <c r="G350" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H350" s="4" t="inlineStr">
@@ -27717,7 +27732,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N350" s="4" t="n">
+      <c r="N350" s="8" t="n">
         <v>2.96696597438552</v>
       </c>
       <c r="O350" s="4" t="inlineStr">
@@ -27763,7 +27778,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G351" s="4" t="n">
+      <c r="G351" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H351" s="4" t="inlineStr">
@@ -27796,7 +27811,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N351" s="4" t="n">
+      <c r="N351" s="8" t="n">
         <v>2.9395819591844</v>
       </c>
       <c r="O351" s="4" t="inlineStr">
@@ -27842,7 +27857,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G352" s="4" t="n">
+      <c r="G352" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H352" s="4" t="inlineStr">
@@ -27875,7 +27890,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N352" s="4" t="n">
+      <c r="N352" s="8" t="n">
         <v>2.9216883785441</v>
       </c>
       <c r="O352" s="4" t="inlineStr">
@@ -27921,7 +27936,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G353" s="4" t="n">
+      <c r="G353" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H353" s="4" t="inlineStr">
@@ -27954,7 +27969,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N353" s="4" t="n">
+      <c r="N353" s="8" t="n">
         <v>2.911170001683</v>
       </c>
       <c r="O353" s="4" t="inlineStr">
@@ -28000,7 +28015,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G354" s="4" t="n">
+      <c r="G354" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H354" s="4" t="inlineStr">
@@ -28033,7 +28048,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N354" s="4" t="n">
+      <c r="N354" s="8" t="n">
         <v>2.90120378571083</v>
       </c>
       <c r="O354" s="4" t="inlineStr">
@@ -28079,7 +28094,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G355" s="4" t="n">
+      <c r="G355" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H355" s="4" t="inlineStr">
@@ -28112,7 +28127,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N355" s="4" t="n">
+      <c r="N355" s="8" t="n">
         <v>2.88423643148571</v>
       </c>
       <c r="O355" s="4" t="inlineStr">
@@ -28158,7 +28173,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G356" s="4" t="n">
+      <c r="G356" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H356" s="4" t="inlineStr">
@@ -28191,7 +28206,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N356" s="4" t="n">
+      <c r="N356" s="8" t="n">
         <v>2.85729074115345</v>
       </c>
       <c r="O356" s="4" t="inlineStr">
@@ -28237,7 +28252,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G357" s="4" t="n">
+      <c r="G357" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H357" s="4" t="inlineStr">
@@ -28270,7 +28285,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N357" s="4" t="n">
+      <c r="N357" s="8" t="n">
         <v>2.81591887200814</v>
       </c>
       <c r="O357" s="4" t="inlineStr">
@@ -28316,7 +28331,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G358" s="4" t="n">
+      <c r="G358" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H358" s="4" t="inlineStr">
@@ -28349,7 +28364,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N358" s="4" t="n">
+      <c r="N358" s="8" t="n">
         <v>2.77330334164225</v>
       </c>
       <c r="O358" s="4" t="inlineStr">
@@ -28395,7 +28410,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G359" s="4" t="n">
+      <c r="G359" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H359" s="4" t="inlineStr">
@@ -28428,7 +28443,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N359" s="4" t="n">
+      <c r="N359" s="8" t="n">
         <v>2.73257068541178</v>
       </c>
       <c r="O359" s="4" t="inlineStr">
@@ -28474,7 +28489,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G360" s="4" t="n">
+      <c r="G360" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H360" s="4" t="inlineStr">
@@ -28507,7 +28522,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N360" s="4" t="n">
+      <c r="N360" s="8" t="n">
         <v>2.69463088437118</v>
       </c>
       <c r="O360" s="4" t="inlineStr">
@@ -28553,7 +28568,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G361" s="4" t="n">
+      <c r="G361" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H361" s="4" t="inlineStr">
@@ -28586,7 +28601,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N361" s="4" t="n">
+      <c r="N361" s="8" t="n">
         <v>2.66099754289596</v>
       </c>
       <c r="O361" s="4" t="inlineStr">
@@ -28632,7 +28647,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G362" s="4" t="n">
+      <c r="G362" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H362" s="4" t="inlineStr">
@@ -28665,7 +28680,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N362" s="4" t="n">
+      <c r="N362" s="8" t="n">
         <v>2.62614099270944</v>
       </c>
       <c r="O362" s="4" t="inlineStr">
@@ -28711,7 +28726,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G363" s="4" t="n">
+      <c r="G363" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H363" s="4" t="inlineStr">
@@ -28744,7 +28759,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N363" s="4" t="n">
+      <c r="N363" s="8" t="n">
         <v>2.61200318869266</v>
       </c>
       <c r="O363" s="4" t="inlineStr">
@@ -28790,7 +28805,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G364" s="4" t="n">
+      <c r="G364" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H364" s="4" t="inlineStr">
@@ -28823,7 +28838,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N364" s="4" t="n">
+      <c r="N364" s="8" t="n">
         <v>2.59621676285258</v>
       </c>
       <c r="O364" s="4" t="inlineStr">
@@ -28869,7 +28884,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G365" s="4" t="n">
+      <c r="G365" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H365" s="4" t="inlineStr">
@@ -28902,7 +28917,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N365" s="4" t="n">
+      <c r="N365" s="8" t="n">
         <v>2.5550534835076</v>
       </c>
       <c r="O365" s="4" t="inlineStr">
@@ -28948,7 +28963,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G366" s="4" t="n">
+      <c r="G366" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H366" s="4" t="inlineStr">
@@ -28981,7 +28996,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N366" s="4" t="n">
+      <c r="N366" s="8" t="n">
         <v>2.50092436734704</v>
       </c>
       <c r="O366" s="4" t="inlineStr">
@@ -29027,7 +29042,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G367" s="4" t="n">
+      <c r="G367" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H367" s="4" t="inlineStr">
@@ -29060,7 +29075,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N367" s="4" t="n">
+      <c r="N367" s="8" t="n">
         <v>2.44084938719203</v>
       </c>
       <c r="O367" s="4" t="inlineStr">
@@ -29106,7 +29121,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G368" s="4" t="n">
+      <c r="G368" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H368" s="4" t="inlineStr">
@@ -29139,7 +29154,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N368" s="4" t="n">
+      <c r="N368" s="8" t="n">
         <v>2.38168897149485</v>
       </c>
       <c r="O368" s="4" t="inlineStr">
@@ -29185,7 +29200,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G369" s="4" t="n">
+      <c r="G369" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H369" s="4" t="inlineStr">
@@ -29218,7 +29233,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N369" s="4" t="n">
+      <c r="N369" s="8" t="n">
         <v>2.31745661857209</v>
       </c>
       <c r="O369" s="4" t="inlineStr">
@@ -29264,7 +29279,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G370" s="4" t="n">
+      <c r="G370" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H370" s="4" t="inlineStr">
@@ -29297,7 +29312,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N370" s="4" t="n">
+      <c r="N370" s="8" t="n">
         <v>2.25329732143847</v>
       </c>
       <c r="O370" s="4" t="inlineStr">
@@ -29343,7 +29358,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G371" s="4" t="n">
+      <c r="G371" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H371" s="4" t="inlineStr">
@@ -29376,7 +29391,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N371" s="4" t="n">
+      <c r="N371" s="8" t="n">
         <v>2.19027461047796</v>
       </c>
       <c r="O371" s="4" t="inlineStr">
@@ -29422,7 +29437,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G372" s="4" t="n">
+      <c r="G372" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H372" s="4" t="inlineStr">
@@ -29455,7 +29470,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N372" s="4" t="n">
+      <c r="N372" s="8" t="n">
         <v>2.13415920641198</v>
       </c>
       <c r="O372" s="4" t="inlineStr">
@@ -29501,7 +29516,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G373" s="4" t="n">
+      <c r="G373" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H373" s="4" t="inlineStr">
@@ -29534,7 +29549,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N373" s="4" t="n">
+      <c r="N373" s="8" t="n">
         <v>2.08805824636671</v>
       </c>
       <c r="O373" s="4" t="inlineStr">
@@ -29580,7 +29595,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G374" s="4" t="n">
+      <c r="G374" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H374" s="4" t="inlineStr">
@@ -29613,7 +29628,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N374" s="4" t="n">
+      <c r="N374" s="8" t="n">
         <v>2.05088234370289</v>
       </c>
       <c r="O374" s="4" t="inlineStr">
@@ -29659,7 +29674,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G375" s="4" t="n">
+      <c r="G375" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H375" s="4" t="inlineStr">
@@ -29692,7 +29707,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N375" s="4" t="n">
+      <c r="N375" s="8" t="n">
         <v>2.01000402655574</v>
       </c>
       <c r="O375" s="4" t="inlineStr">
@@ -29738,7 +29753,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G376" s="4" t="n">
+      <c r="G376" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H376" s="4" t="inlineStr">
@@ -29771,7 +29786,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N376" s="4" t="n">
+      <c r="N376" s="8" t="n">
         <v>1.95213333149154</v>
       </c>
       <c r="O376" s="4" t="inlineStr">
@@ -29817,7 +29832,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G377" s="4" t="n">
+      <c r="G377" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H377" s="4" t="inlineStr">
@@ -29850,7 +29865,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N377" s="4" t="n">
+      <c r="N377" s="8" t="n">
         <v>1.89379499634952</v>
       </c>
       <c r="O377" s="4" t="inlineStr">
@@ -29896,7 +29911,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G378" s="4" t="n">
+      <c r="G378" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H378" s="4" t="inlineStr">
@@ -29929,7 +29944,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N378" s="4" t="n">
+      <c r="N378" s="8" t="n">
         <v>1.83097359469052</v>
       </c>
       <c r="O378" s="4" t="inlineStr">
@@ -29975,7 +29990,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G379" s="4" t="n">
+      <c r="G379" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H379" s="4" t="inlineStr">
@@ -30008,7 +30023,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N379" s="4" t="n">
+      <c r="N379" s="8" t="n">
         <v>1.80801767033013</v>
       </c>
       <c r="O379" s="4" t="inlineStr">
@@ -30054,7 +30069,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G380" s="4" t="n">
+      <c r="G380" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H380" s="4" t="inlineStr">
@@ -30087,7 +30102,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N380" s="4" t="n">
+      <c r="N380" s="8" t="n">
         <v>1.78086326604433</v>
       </c>
       <c r="O380" s="4" t="inlineStr">
@@ -30133,7 +30148,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G381" s="4" t="n">
+      <c r="G381" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H381" s="4" t="inlineStr">
@@ -30166,7 +30181,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N381" s="4" t="n">
+      <c r="N381" s="8" t="n">
         <v>1.71593189812023</v>
       </c>
       <c r="O381" s="4" t="inlineStr">
@@ -30212,7 +30227,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G382" s="4" t="n">
+      <c r="G382" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H382" s="4" t="inlineStr">
@@ -30245,7 +30260,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N382" s="4" t="n">
+      <c r="N382" s="8" t="n">
         <v>1.67515351433713</v>
       </c>
       <c r="O382" s="4" t="inlineStr">
@@ -30291,7 +30306,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G383" s="4" t="n">
+      <c r="G383" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H383" s="4" t="inlineStr">
@@ -30324,7 +30339,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N383" s="4" t="n">
+      <c r="N383" s="8" t="n">
         <v>1.62520895526481</v>
       </c>
       <c r="O383" s="4" t="inlineStr">
@@ -30370,7 +30385,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G384" s="4" t="n">
+      <c r="G384" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H384" s="4" t="inlineStr">
@@ -30403,7 +30418,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N384" s="4" t="n">
+      <c r="N384" s="8" t="n">
         <v>1.54785544927575</v>
       </c>
       <c r="O384" s="4" t="inlineStr">
@@ -30449,7 +30464,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G385" s="4" t="n">
+      <c r="G385" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H385" s="4" t="inlineStr">
@@ -30482,7 +30497,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N385" s="4" t="n">
+      <c r="N385" s="8" t="n">
         <v>1.45176982660994</v>
       </c>
       <c r="O385" s="4" t="inlineStr">
@@ -30528,7 +30543,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G386" s="4" t="n">
+      <c r="G386" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H386" s="4" t="inlineStr">
@@ -30561,7 +30576,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N386" s="4" t="n">
+      <c r="N386" s="8" t="n">
         <v>1.36163698615317</v>
       </c>
       <c r="O386" s="4" t="inlineStr">
@@ -30607,7 +30622,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G387" s="4" t="n">
+      <c r="G387" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H387" s="4" t="inlineStr">
@@ -30640,7 +30655,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N387" s="4" t="n">
+      <c r="N387" s="8" t="n">
         <v>1.30934216855774</v>
       </c>
       <c r="O387" s="4" t="inlineStr">
@@ -30686,7 +30701,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G388" s="4" t="n">
+      <c r="G388" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H388" s="4" t="inlineStr">
@@ -30719,7 +30734,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N388" s="4" t="n">
+      <c r="N388" s="8" t="n">
         <v>1.28319630933634</v>
       </c>
       <c r="O388" s="4" t="inlineStr">
@@ -30765,7 +30780,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G389" s="4" t="n">
+      <c r="G389" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H389" s="4" t="inlineStr">
@@ -30798,7 +30813,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N389" s="4" t="n">
+      <c r="N389" s="8" t="n">
         <v>1.25510683013417</v>
       </c>
       <c r="O389" s="4" t="inlineStr">
@@ -30844,7 +30859,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G390" s="4" t="n">
+      <c r="G390" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H390" s="4" t="inlineStr">
@@ -30877,7 +30892,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N390" s="4" t="n">
+      <c r="N390" s="8" t="n">
         <v>1.20531461336652</v>
       </c>
       <c r="O390" s="4" t="inlineStr">
@@ -30923,7 +30938,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G391" s="4" t="n">
+      <c r="G391" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H391" s="4" t="inlineStr">
@@ -30956,7 +30971,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N391" s="4" t="n">
+      <c r="N391" s="8" t="n">
         <v>1.13646612916995</v>
       </c>
       <c r="O391" s="4" t="inlineStr">
@@ -31002,7 +31017,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G392" s="4" t="n">
+      <c r="G392" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H392" s="4" t="inlineStr">
@@ -31035,7 +31050,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N392" s="4" t="n">
+      <c r="N392" s="8" t="n">
         <v>1.0518040406043</v>
       </c>
       <c r="O392" s="4" t="inlineStr">
@@ -31081,7 +31096,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G393" s="4" t="n">
+      <c r="G393" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H393" s="4" t="inlineStr">
@@ -31114,7 +31129,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N393" s="4" t="n">
+      <c r="N393" s="8" t="n">
         <v>0.62520243689416</v>
       </c>
       <c r="O393" s="4" t="inlineStr">
@@ -31160,7 +31175,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G394" s="4" t="n">
+      <c r="G394" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H394" s="4" t="inlineStr">
@@ -31193,7 +31208,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N394" s="4" t="n">
+      <c r="N394" s="8" t="n">
         <v>-0.653495206896492</v>
       </c>
       <c r="O394" s="4" t="inlineStr">
@@ -31239,7 +31254,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G395" s="4" t="n">
+      <c r="G395" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H395" s="4" t="inlineStr">
@@ -31272,7 +31287,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N395" s="4" t="n">
+      <c r="N395" s="8" t="n">
         <v>-2.51030049026678</v>
       </c>
       <c r="O395" s="4" t="inlineStr">
@@ -31318,7 +31333,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G396" s="4" t="n">
+      <c r="G396" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H396" s="4" t="inlineStr">
@@ -31351,7 +31366,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N396" s="4" t="n">
+      <c r="N396" s="8" t="n">
         <v>-2.96041293052007</v>
       </c>
       <c r="O396" s="4" t="inlineStr">
@@ -31397,7 +31412,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G397" s="4" t="n">
+      <c r="G397" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H397" s="4" t="inlineStr">
@@ -31430,7 +31445,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N397" s="4" t="n">
+      <c r="N397" s="8" t="n">
         <v>-1.72190477685565</v>
       </c>
       <c r="O397" s="4" t="inlineStr">
@@ -31476,7 +31491,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G398" s="4" t="n">
+      <c r="G398" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H398" s="4" t="inlineStr">
@@ -31509,7 +31524,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N398" s="4" t="n">
+      <c r="N398" s="8" t="n">
         <v>-0.727752243229035</v>
       </c>
       <c r="O398" s="4" t="inlineStr">
@@ -31555,7 +31570,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G399" s="4" t="n">
+      <c r="G399" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H399" s="4" t="inlineStr">
@@ -31588,7 +31603,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N399" s="4" t="n">
+      <c r="N399" s="8" t="n">
         <v>-0.08789594726592299</v>
       </c>
       <c r="O399" s="4" t="inlineStr">
@@ -31634,7 +31649,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G400" s="4" t="n">
+      <c r="G400" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H400" s="4" t="inlineStr">
@@ -31667,7 +31682,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N400" s="4" t="n">
+      <c r="N400" s="8" t="n">
         <v>0.310851368612458</v>
       </c>
       <c r="O400" s="4" t="inlineStr">
@@ -31713,7 +31728,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G401" s="4" t="n">
+      <c r="G401" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H401" s="4" t="inlineStr">
@@ -31746,7 +31761,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N401" s="4" t="n">
+      <c r="N401" s="8" t="n">
         <v>0.369232130679939</v>
       </c>
       <c r="O401" s="4" t="inlineStr">
@@ -31792,7 +31807,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G402" s="4" t="n">
+      <c r="G402" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H402" s="4" t="inlineStr">
@@ -31825,7 +31840,7 @@
           <t>Crecimiento anual de la población</t>
         </is>
       </c>
-      <c r="N402" s="4" t="n">
+      <c r="N402" s="8" t="n">
         <v>0.39124515392802</v>
       </c>
       <c r="O402" s="4" t="inlineStr">
@@ -31871,7 +31886,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G403" s="4" t="n">
+      <c r="G403" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H403" s="4" t="inlineStr">
@@ -31904,7 +31919,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N403" s="4" t="n">
+      <c r="N403" s="7" t="n">
         <v>8160090</v>
       </c>
       <c r="O403" s="4" t="inlineStr">
@@ -31950,7 +31965,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G404" s="4" t="n">
+      <c r="G404" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H404" s="4" t="inlineStr">
@@ -31983,7 +31998,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N404" s="4" t="n">
+      <c r="N404" s="7" t="n">
         <v>8455915</v>
       </c>
       <c r="O404" s="4" t="inlineStr">
@@ -32029,7 +32044,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G405" s="4" t="n">
+      <c r="G405" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H405" s="4" t="inlineStr">
@@ -32062,7 +32077,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N405" s="4" t="n">
+      <c r="N405" s="7" t="n">
         <v>8756870</v>
       </c>
       <c r="O405" s="4" t="inlineStr">
@@ -32108,7 +32123,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G406" s="4" t="n">
+      <c r="G406" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H406" s="4" t="inlineStr">
@@ -32141,7 +32156,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N406" s="4" t="n">
+      <c r="N406" s="7" t="n">
         <v>9064021</v>
       </c>
       <c r="O406" s="4" t="inlineStr">
@@ -32187,7 +32202,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G407" s="4" t="n">
+      <c r="G407" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H407" s="4" t="inlineStr">
@@ -32220,7 +32235,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N407" s="4" t="n">
+      <c r="N407" s="7" t="n">
         <v>9377712</v>
       </c>
       <c r="O407" s="4" t="inlineStr">
@@ -32266,7 +32281,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G408" s="4" t="n">
+      <c r="G408" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H408" s="4" t="inlineStr">
@@ -32299,7 +32314,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N408" s="4" t="n">
+      <c r="N408" s="7" t="n">
         <v>9697790</v>
       </c>
       <c r="O408" s="4" t="inlineStr">
@@ -32345,7 +32360,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G409" s="4" t="n">
+      <c r="G409" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H409" s="4" t="inlineStr">
@@ -32378,7 +32393,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N409" s="4" t="n">
+      <c r="N409" s="7" t="n">
         <v>10024854</v>
       </c>
       <c r="O409" s="4" t="inlineStr">
@@ -32424,7 +32439,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G410" s="4" t="n">
+      <c r="G410" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H410" s="4" t="inlineStr">
@@ -32457,7 +32472,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N410" s="4" t="n">
+      <c r="N410" s="7" t="n">
         <v>10358513</v>
       </c>
       <c r="O410" s="4" t="inlineStr">
@@ -32503,7 +32518,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G411" s="4" t="n">
+      <c r="G411" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H411" s="4" t="inlineStr">
@@ -32536,7 +32551,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N411" s="4" t="n">
+      <c r="N411" s="7" t="n">
         <v>10697530</v>
       </c>
       <c r="O411" s="4" t="inlineStr">
@@ -32582,7 +32597,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G412" s="4" t="n">
+      <c r="G412" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H412" s="4" t="inlineStr">
@@ -32615,7 +32630,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N412" s="4" t="n">
+      <c r="N412" s="7" t="n">
         <v>11040280</v>
       </c>
       <c r="O412" s="4" t="inlineStr">
@@ -32661,7 +32676,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G413" s="4" t="n">
+      <c r="G413" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H413" s="4" t="inlineStr">
@@ -32694,7 +32709,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N413" s="4" t="n">
+      <c r="N413" s="7" t="n">
         <v>11387790</v>
       </c>
       <c r="O413" s="4" t="inlineStr">
@@ -32740,7 +32755,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G414" s="4" t="n">
+      <c r="G414" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H414" s="4" t="inlineStr">
@@ -32773,7 +32788,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N414" s="4" t="n">
+      <c r="N414" s="7" t="n">
         <v>11741008</v>
       </c>
       <c r="O414" s="4" t="inlineStr">
@@ -32819,7 +32834,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G415" s="4" t="n">
+      <c r="G415" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H415" s="4" t="inlineStr">
@@ -32852,7 +32867,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N415" s="4" t="n">
+      <c r="N415" s="7" t="n">
         <v>12099180</v>
       </c>
       <c r="O415" s="4" t="inlineStr">
@@ -32898,7 +32913,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G416" s="4" t="n">
+      <c r="G416" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H416" s="4" t="inlineStr">
@@ -32931,7 +32946,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N416" s="4" t="n">
+      <c r="N416" s="7" t="n">
         <v>12463537</v>
       </c>
       <c r="O416" s="4" t="inlineStr">
@@ -32977,7 +32992,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G417" s="4" t="n">
+      <c r="G417" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H417" s="4" t="inlineStr">
@@ -33010,7 +33025,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N417" s="4" t="n">
+      <c r="N417" s="7" t="n">
         <v>12835351</v>
       </c>
       <c r="O417" s="4" t="inlineStr">
@@ -33056,7 +33071,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G418" s="4" t="n">
+      <c r="G418" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H418" s="4" t="inlineStr">
@@ -33089,7 +33104,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N418" s="4" t="n">
+      <c r="N418" s="7" t="n">
         <v>13215892</v>
       </c>
       <c r="O418" s="4" t="inlineStr">
@@ -33135,7 +33150,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G419" s="4" t="n">
+      <c r="G419" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H419" s="4" t="inlineStr">
@@ -33168,7 +33183,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N419" s="4" t="n">
+      <c r="N419" s="7" t="n">
         <v>13606284</v>
       </c>
       <c r="O419" s="4" t="inlineStr">
@@ -33214,7 +33229,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G420" s="4" t="n">
+      <c r="G420" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H420" s="4" t="inlineStr">
@@ -33247,7 +33262,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N420" s="4" t="n">
+      <c r="N420" s="7" t="n">
         <v>14006812</v>
       </c>
       <c r="O420" s="4" t="inlineStr">
@@ -33293,7 +33308,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G421" s="4" t="n">
+      <c r="G421" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H421" s="4" t="inlineStr">
@@ -33326,7 +33341,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N421" s="4" t="n">
+      <c r="N421" s="7" t="n">
         <v>14416684</v>
       </c>
       <c r="O421" s="4" t="inlineStr">
@@ -33372,7 +33387,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G422" s="4" t="n">
+      <c r="G422" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H422" s="4" t="inlineStr">
@@ -33405,7 +33420,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N422" s="4" t="n">
+      <c r="N422" s="7" t="n">
         <v>14834552</v>
       </c>
       <c r="O422" s="4" t="inlineStr">
@@ -33451,7 +33466,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G423" s="4" t="n">
+      <c r="G423" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H423" s="4" t="inlineStr">
@@ -33484,7 +33499,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N423" s="4" t="n">
+      <c r="N423" s="7" t="n">
         <v>15258218</v>
       </c>
       <c r="O423" s="4" t="inlineStr">
@@ -33530,7 +33545,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G424" s="4" t="n">
+      <c r="G424" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H424" s="4" t="inlineStr">
@@ -33563,7 +33578,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N424" s="4" t="n">
+      <c r="N424" s="7" t="n">
         <v>15687297</v>
       </c>
       <c r="O424" s="4" t="inlineStr">
@@ -33609,7 +33624,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G425" s="4" t="n">
+      <c r="G425" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H425" s="4" t="inlineStr">
@@ -33642,7 +33657,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N425" s="4" t="n">
+      <c r="N425" s="7" t="n">
         <v>16121874</v>
       </c>
       <c r="O425" s="4" t="inlineStr">
@@ -33688,7 +33703,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G426" s="4" t="n">
+      <c r="G426" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H426" s="4" t="inlineStr">
@@ -33721,7 +33736,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N426" s="4" t="n">
+      <c r="N426" s="7" t="n">
         <v>16562205</v>
       </c>
       <c r="O426" s="4" t="inlineStr">
@@ -33767,7 +33782,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G427" s="4" t="n">
+      <c r="G427" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H427" s="4" t="inlineStr">
@@ -33800,7 +33815,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N427" s="4" t="n">
+      <c r="N427" s="7" t="n">
         <v>17008841</v>
       </c>
       <c r="O427" s="4" t="inlineStr">
@@ -33846,7 +33861,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G428" s="4" t="n">
+      <c r="G428" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H428" s="4" t="inlineStr">
@@ -33879,7 +33894,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N428" s="4" t="n">
+      <c r="N428" s="7" t="n">
         <v>17461434</v>
       </c>
       <c r="O428" s="4" t="inlineStr">
@@ -33925,7 +33940,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G429" s="4" t="n">
+      <c r="G429" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H429" s="4" t="inlineStr">
@@ -33958,7 +33973,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N429" s="4" t="n">
+      <c r="N429" s="7" t="n">
         <v>17923536</v>
       </c>
       <c r="O429" s="4" t="inlineStr">
@@ -34004,7 +34019,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G430" s="4" t="n">
+      <c r="G430" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H430" s="4" t="inlineStr">
@@ -34037,7 +34052,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N430" s="4" t="n">
+      <c r="N430" s="7" t="n">
         <v>18394963</v>
       </c>
       <c r="O430" s="4" t="inlineStr">
@@ -34083,7 +34098,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G431" s="4" t="n">
+      <c r="G431" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H431" s="4" t="inlineStr">
@@ -34116,7 +34131,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N431" s="4" t="n">
+      <c r="N431" s="7" t="n">
         <v>18871020</v>
       </c>
       <c r="O431" s="4" t="inlineStr">
@@ -34162,7 +34177,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G432" s="4" t="n">
+      <c r="G432" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H432" s="4" t="inlineStr">
@@ -34195,7 +34210,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N432" s="4" t="n">
+      <c r="N432" s="7" t="n">
         <v>19348921</v>
       </c>
       <c r="O432" s="4" t="inlineStr">
@@ -34241,7 +34256,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G433" s="4" t="n">
+      <c r="G433" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H433" s="4" t="inlineStr">
@@ -34274,7 +34289,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N433" s="4" t="n">
+      <c r="N433" s="7" t="n">
         <v>19827010</v>
       </c>
       <c r="O433" s="4" t="inlineStr">
@@ -34320,7 +34335,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G434" s="4" t="n">
+      <c r="G434" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H434" s="4" t="inlineStr">
@@ -34353,7 +34368,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N434" s="4" t="n">
+      <c r="N434" s="7" t="n">
         <v>20304896</v>
       </c>
       <c r="O434" s="4" t="inlineStr">
@@ -34399,7 +34414,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G435" s="4" t="n">
+      <c r="G435" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H435" s="4" t="inlineStr">
@@ -34432,7 +34447,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N435" s="4" t="n">
+      <c r="N435" s="7" t="n">
         <v>20780948</v>
       </c>
       <c r="O435" s="4" t="inlineStr">
@@ -34478,7 +34493,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G436" s="4" t="n">
+      <c r="G436" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H436" s="4" t="inlineStr">
@@ -34511,7 +34526,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N436" s="4" t="n">
+      <c r="N436" s="7" t="n">
         <v>21254520</v>
       </c>
       <c r="O436" s="4" t="inlineStr">
@@ -34557,7 +34572,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G437" s="4" t="n">
+      <c r="G437" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H437" s="4" t="inlineStr">
@@ -34590,7 +34605,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N437" s="4" t="n">
+      <c r="N437" s="7" t="n">
         <v>21725188</v>
       </c>
       <c r="O437" s="4" t="inlineStr">
@@ -34636,7 +34651,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G438" s="4" t="n">
+      <c r="G438" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H438" s="4" t="inlineStr">
@@ -34669,7 +34684,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N438" s="4" t="n">
+      <c r="N438" s="7" t="n">
         <v>22193821</v>
       </c>
       <c r="O438" s="4" t="inlineStr">
@@ -34715,7 +34730,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G439" s="4" t="n">
+      <c r="G439" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H439" s="4" t="inlineStr">
@@ -34748,7 +34763,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N439" s="4" t="n">
+      <c r="N439" s="7" t="n">
         <v>22662113</v>
       </c>
       <c r="O439" s="4" t="inlineStr">
@@ -34794,7 +34809,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G440" s="4" t="n">
+      <c r="G440" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H440" s="4" t="inlineStr">
@@ -34827,7 +34842,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N440" s="4" t="n">
+      <c r="N440" s="7" t="n">
         <v>23131685</v>
       </c>
       <c r="O440" s="4" t="inlineStr">
@@ -34873,7 +34888,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G441" s="4" t="n">
+      <c r="G441" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H441" s="4" t="inlineStr">
@@ -34906,7 +34921,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N441" s="4" t="n">
+      <c r="N441" s="7" t="n">
         <v>23601337</v>
       </c>
       <c r="O441" s="4" t="inlineStr">
@@ -34952,7 +34967,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G442" s="4" t="n">
+      <c r="G442" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H442" s="4" t="inlineStr">
@@ -34985,7 +35000,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N442" s="4" t="n">
+      <c r="N442" s="7" t="n">
         <v>24066593</v>
       </c>
       <c r="O442" s="4" t="inlineStr">
@@ -35031,7 +35046,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G443" s="4" t="n">
+      <c r="G443" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H443" s="4" t="inlineStr">
@@ -35064,7 +35079,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N443" s="4" t="n">
+      <c r="N443" s="7" t="n">
         <v>24526708</v>
       </c>
       <c r="O443" s="4" t="inlineStr">
@@ -35110,7 +35125,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G444" s="4" t="n">
+      <c r="G444" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H444" s="4" t="inlineStr">
@@ -35143,7 +35158,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N444" s="4" t="n">
+      <c r="N444" s="7" t="n">
         <v>24979922</v>
       </c>
       <c r="O444" s="4" t="inlineStr">
@@ -35189,7 +35204,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G445" s="4" t="n">
+      <c r="G445" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H445" s="4" t="inlineStr">
@@ -35222,7 +35237,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N445" s="4" t="n">
+      <c r="N445" s="7" t="n">
         <v>25435671</v>
       </c>
       <c r="O445" s="4" t="inlineStr">
@@ -35268,7 +35283,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G446" s="4" t="n">
+      <c r="G446" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H446" s="4" t="inlineStr">
@@ -35301,7 +35316,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N446" s="4" t="n">
+      <c r="N446" s="7" t="n">
         <v>25892703</v>
       </c>
       <c r="O446" s="4" t="inlineStr">
@@ -35347,7 +35362,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G447" s="4" t="n">
+      <c r="G447" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H447" s="4" t="inlineStr">
@@ -35380,7 +35395,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N447" s="4" t="n">
+      <c r="N447" s="7" t="n">
         <v>26340838</v>
       </c>
       <c r="O447" s="4" t="inlineStr">
@@ -35426,7 +35441,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G448" s="4" t="n">
+      <c r="G448" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H448" s="4" t="inlineStr">
@@ -35459,7 +35474,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N448" s="4" t="n">
+      <c r="N448" s="7" t="n">
         <v>26785804</v>
       </c>
       <c r="O448" s="4" t="inlineStr">
@@ -35505,7 +35520,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G449" s="4" t="n">
+      <c r="G449" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H449" s="4" t="inlineStr">
@@ -35538,7 +35553,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N449" s="4" t="n">
+      <c r="N449" s="7" t="n">
         <v>27224686</v>
       </c>
       <c r="O449" s="4" t="inlineStr">
@@ -35584,7 +35599,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G450" s="4" t="n">
+      <c r="G450" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H450" s="4" t="inlineStr">
@@ -35617,7 +35632,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N450" s="4" t="n">
+      <c r="N450" s="7" t="n">
         <v>27649363</v>
       </c>
       <c r="O450" s="4" t="inlineStr">
@@ -35663,7 +35678,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G451" s="4" t="n">
+      <c r="G451" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H451" s="4" t="inlineStr">
@@ -35696,7 +35711,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N451" s="4" t="n">
+      <c r="N451" s="7" t="n">
         <v>28053696</v>
       </c>
       <c r="O451" s="4" t="inlineStr">
@@ -35742,7 +35757,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G452" s="4" t="n">
+      <c r="G452" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H452" s="4" t="inlineStr">
@@ -35775,7 +35790,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N452" s="4" t="n">
+      <c r="N452" s="7" t="n">
         <v>28438298</v>
       </c>
       <c r="O452" s="4" t="inlineStr">
@@ -35821,7 +35836,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G453" s="4" t="n">
+      <c r="G453" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H453" s="4" t="inlineStr">
@@ -35854,7 +35869,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N453" s="4" t="n">
+      <c r="N453" s="7" t="n">
         <v>28813101</v>
       </c>
       <c r="O453" s="4" t="inlineStr">
@@ -35900,7 +35915,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G454" s="4" t="n">
+      <c r="G454" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H454" s="4" t="inlineStr">
@@ -35933,7 +35948,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N454" s="4" t="n">
+      <c r="N454" s="7" t="n">
         <v>29185212</v>
       </c>
       <c r="O454" s="4" t="inlineStr">
@@ -35979,7 +35994,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G455" s="4" t="n">
+      <c r="G455" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H455" s="4" t="inlineStr">
@@ -36012,7 +36027,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N455" s="4" t="n">
+      <c r="N455" s="7" t="n">
         <v>29553826</v>
       </c>
       <c r="O455" s="4" t="inlineStr">
@@ -36058,7 +36073,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G456" s="4" t="n">
+      <c r="G456" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H456" s="4" t="inlineStr">
@@ -36091,7 +36106,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N456" s="4" t="n">
+      <c r="N456" s="7" t="n">
         <v>29912198</v>
       </c>
       <c r="O456" s="4" t="inlineStr">
@@ -36137,7 +36152,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G457" s="4" t="n">
+      <c r="G457" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H457" s="4" t="inlineStr">
@@ -36170,7 +36185,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N457" s="4" t="n">
+      <c r="N457" s="7" t="n">
         <v>30254079</v>
       </c>
       <c r="O457" s="4" t="inlineStr">
@@ -36216,7 +36231,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G458" s="4" t="n">
+      <c r="G458" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H458" s="4" t="inlineStr">
@@ -36249,7 +36264,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N458" s="4" t="n">
+      <c r="N458" s="7" t="n">
         <v>30573972</v>
       </c>
       <c r="O458" s="4" t="inlineStr">
@@ -36295,7 +36310,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G459" s="4" t="n">
+      <c r="G459" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H459" s="4" t="inlineStr">
@@ -36328,7 +36343,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N459" s="4" t="n">
+      <c r="N459" s="7" t="n">
         <v>30765720</v>
       </c>
       <c r="O459" s="4" t="inlineStr">
@@ -36374,7 +36389,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G460" s="4" t="n">
+      <c r="G460" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H460" s="4" t="inlineStr">
@@ -36407,7 +36422,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N460" s="4" t="n">
+      <c r="N460" s="7" t="n">
         <v>30565323</v>
       </c>
       <c r="O460" s="4" t="inlineStr">
@@ -36453,7 +36468,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G461" s="4" t="n">
+      <c r="G461" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H461" s="4" t="inlineStr">
@@ -36486,7 +36501,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N461" s="4" t="n">
+      <c r="N461" s="7" t="n">
         <v>29807592</v>
       </c>
       <c r="O461" s="4" t="inlineStr">
@@ -36532,7 +36547,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G462" s="4" t="n">
+      <c r="G462" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H462" s="4" t="inlineStr">
@@ -36565,7 +36580,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N462" s="4" t="n">
+      <c r="N462" s="7" t="n">
         <v>28938098</v>
       </c>
       <c r="O462" s="4" t="inlineStr">
@@ -36611,7 +36626,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G463" s="4" t="n">
+      <c r="G463" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H463" s="4" t="inlineStr">
@@ -36644,7 +36659,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N463" s="4" t="n">
+      <c r="N463" s="7" t="n">
         <v>28444077</v>
       </c>
       <c r="O463" s="4" t="inlineStr">
@@ -36690,7 +36705,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G464" s="4" t="n">
+      <c r="G464" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H464" s="4" t="inlineStr">
@@ -36723,7 +36738,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N464" s="4" t="n">
+      <c r="N464" s="7" t="n">
         <v>28237826</v>
       </c>
       <c r="O464" s="4" t="inlineStr">
@@ -36769,7 +36784,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G465" s="4" t="n">
+      <c r="G465" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H465" s="4" t="inlineStr">
@@ -36802,7 +36817,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N465" s="4" t="n">
+      <c r="N465" s="7" t="n">
         <v>28213017</v>
       </c>
       <c r="O465" s="4" t="inlineStr">
@@ -36848,7 +36863,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G466" s="4" t="n">
+      <c r="G466" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H466" s="4" t="inlineStr">
@@ -36881,7 +36896,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N466" s="4" t="n">
+      <c r="N466" s="7" t="n">
         <v>28300854</v>
       </c>
       <c r="O466" s="4" t="inlineStr">
@@ -36927,7 +36942,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G467" s="4" t="n">
+      <c r="G467" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H467" s="4" t="inlineStr">
@@ -36960,7 +36975,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N467" s="4" t="n">
+      <c r="N467" s="7" t="n">
         <v>28405543</v>
       </c>
       <c r="O467" s="4" t="inlineStr">
@@ -37006,7 +37021,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G468" s="4" t="n">
+      <c r="G468" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H468" s="4" t="inlineStr">
@@ -37039,7 +37054,7 @@
           <t>Población total</t>
         </is>
       </c>
-      <c r="N468" s="4" t="n">
+      <c r="N468" s="7" t="n">
         <v>28516896</v>
       </c>
       <c r="O468" s="4" t="inlineStr">
@@ -37085,7 +37100,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G469" s="4" t="n">
+      <c r="G469" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H469" s="4" t="inlineStr">
@@ -37118,7 +37133,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N469" s="4" t="n">
+      <c r="N469" s="8" t="n">
         <v>61.9199514882795</v>
       </c>
       <c r="O469" s="4" t="inlineStr">
@@ -37164,7 +37179,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G470" s="4" t="n">
+      <c r="G470" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H470" s="4" t="inlineStr">
@@ -37197,7 +37212,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N470" s="4" t="n">
+      <c r="N470" s="8" t="n">
         <v>62.8367548343614</v>
       </c>
       <c r="O470" s="4" t="inlineStr">
@@ -37243,7 +37258,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G471" s="4" t="n">
+      <c r="G471" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H471" s="4" t="inlineStr">
@@ -37276,7 +37291,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N471" s="4" t="n">
+      <c r="N471" s="8" t="n">
         <v>63.7926841478446</v>
       </c>
       <c r="O471" s="4" t="inlineStr">
@@ -37322,7 +37337,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G472" s="4" t="n">
+      <c r="G472" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H472" s="4" t="inlineStr">
@@ -37355,7 +37370,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N472" s="4" t="n">
+      <c r="N472" s="8" t="n">
         <v>64.7948953928115</v>
       </c>
       <c r="O472" s="4" t="inlineStr">
@@ -37401,7 +37416,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G473" s="4" t="n">
+      <c r="G473" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H473" s="4" t="inlineStr">
@@ -37434,7 +37449,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N473" s="4" t="n">
+      <c r="N473" s="8" t="n">
         <v>65.8271577115279</v>
       </c>
       <c r="O473" s="4" t="inlineStr">
@@ -37480,7 +37495,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G474" s="4" t="n">
+      <c r="G474" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H474" s="4" t="inlineStr">
@@ -37513,7 +37528,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N474" s="4" t="n">
+      <c r="N474" s="8" t="n">
         <v>66.876288859656</v>
       </c>
       <c r="O474" s="4" t="inlineStr">
@@ -37559,7 +37574,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G475" s="4" t="n">
+      <c r="G475" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H475" s="4" t="inlineStr">
@@ -37592,7 +37607,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N475" s="4" t="n">
+      <c r="N475" s="8" t="n">
         <v>67.9291065928583</v>
       </c>
       <c r="O475" s="4" t="inlineStr">
@@ -37638,7 +37653,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G476" s="4" t="n">
+      <c r="G476" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H476" s="4" t="inlineStr">
@@ -37671,7 +37686,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N476" s="4" t="n">
+      <c r="N476" s="8" t="n">
         <v>68.9724286667969</v>
       </c>
       <c r="O476" s="4" t="inlineStr">
@@ -37717,7 +37732,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G477" s="4" t="n">
+      <c r="G477" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H477" s="4" t="inlineStr">
@@ -37750,7 +37765,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N477" s="4" t="n">
+      <c r="N477" s="8" t="n">
         <v>69.99307283713431</v>
       </c>
       <c r="O477" s="4" t="inlineStr">
@@ -37796,7 +37811,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G478" s="4" t="n">
+      <c r="G478" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H478" s="4" t="inlineStr">
@@ -37829,7 +37844,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N478" s="4" t="n">
+      <c r="N478" s="8" t="n">
         <v>70.97785685953259</v>
       </c>
       <c r="O478" s="4" t="inlineStr">
@@ -37875,7 +37890,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G479" s="4" t="n">
+      <c r="G479" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H479" s="4" t="inlineStr">
@@ -37908,7 +37923,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N479" s="4" t="n">
+      <c r="N479" s="8" t="n">
         <v>71.91359848965411</v>
       </c>
       <c r="O479" s="4" t="inlineStr">
@@ -37954,7 +37969,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G480" s="4" t="n">
+      <c r="G480" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H480" s="4" t="inlineStr">
@@ -37987,7 +38002,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N480" s="4" t="n">
+      <c r="N480" s="8" t="n">
         <v>72.7833152048506</v>
       </c>
       <c r="O480" s="4" t="inlineStr">
@@ -38033,7 +38048,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G481" s="4" t="n">
+      <c r="G481" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H481" s="4" t="inlineStr">
@@ -38066,7 +38081,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N481" s="4" t="n">
+      <c r="N481" s="8" t="n">
         <v>73.5987755273193</v>
       </c>
       <c r="O481" s="4" t="inlineStr">
@@ -38112,7 +38127,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G482" s="4" t="n">
+      <c r="G482" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H482" s="4" t="inlineStr">
@@ -38145,7 +38160,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N482" s="4" t="n">
+      <c r="N482" s="8" t="n">
         <v>74.38605880253139</v>
       </c>
       <c r="O482" s="4" t="inlineStr">
@@ -38191,7 +38206,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G483" s="4" t="n">
+      <c r="G483" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H483" s="4" t="inlineStr">
@@ -38224,7 +38239,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N483" s="4" t="n">
+      <c r="N483" s="8" t="n">
         <v>75.15116097884069</v>
       </c>
       <c r="O483" s="4" t="inlineStr">
@@ -38270,7 +38285,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G484" s="4" t="n">
+      <c r="G484" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H484" s="4" t="inlineStr">
@@ -38303,7 +38318,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N484" s="4" t="n">
+      <c r="N484" s="8" t="n">
         <v>75.8928952206553</v>
       </c>
       <c r="O484" s="4" t="inlineStr">
@@ -38349,7 +38364,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G485" s="4" t="n">
+      <c r="G485" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H485" s="4" t="inlineStr">
@@ -38382,7 +38397,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N485" s="4" t="n">
+      <c r="N485" s="8" t="n">
         <v>76.61007469238341</v>
       </c>
       <c r="O485" s="4" t="inlineStr">
@@ -38428,7 +38443,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G486" s="4" t="n">
+      <c r="G486" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H486" s="4" t="inlineStr">
@@ -38461,7 +38476,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N486" s="4" t="n">
+      <c r="N486" s="8" t="n">
         <v>77.3015125584334</v>
       </c>
       <c r="O486" s="4" t="inlineStr">
@@ -38507,7 +38522,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G487" s="4" t="n">
+      <c r="G487" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H487" s="4" t="inlineStr">
@@ -38540,7 +38555,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N487" s="4" t="n">
+      <c r="N487" s="8" t="n">
         <v>77.96602198321339</v>
       </c>
       <c r="O487" s="4" t="inlineStr">
@@ -38586,7 +38601,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G488" s="4" t="n">
+      <c r="G488" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H488" s="4" t="inlineStr">
@@ -38619,7 +38634,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N488" s="4" t="n">
+      <c r="N488" s="8" t="n">
         <v>78.6024161311317</v>
       </c>
       <c r="O488" s="4" t="inlineStr">
@@ -38665,7 +38680,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G489" s="4" t="n">
+      <c r="G489" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H489" s="4" t="inlineStr">
@@ -38698,7 +38713,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N489" s="4" t="n">
+      <c r="N489" s="8" t="n">
         <v>79.20950816659639</v>
       </c>
       <c r="O489" s="4" t="inlineStr">
@@ -38744,7 +38759,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G490" s="4" t="n">
+      <c r="G490" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H490" s="4" t="inlineStr">
@@ -38777,7 +38792,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N490" s="4" t="n">
+      <c r="N490" s="8" t="n">
         <v>79.7854629662589</v>
       </c>
       <c r="O490" s="4" t="inlineStr">
@@ -38823,7 +38838,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G491" s="4" t="n">
+      <c r="G491" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H491" s="4" t="inlineStr">
@@ -38856,7 +38871,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N491" s="4" t="n">
+      <c r="N491" s="8" t="n">
         <v>80.3313667107622</v>
       </c>
       <c r="O491" s="4" t="inlineStr">
@@ -38902,7 +38917,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G492" s="4" t="n">
+      <c r="G492" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H492" s="4" t="inlineStr">
@@ -38935,7 +38950,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N492" s="4" t="n">
+      <c r="N492" s="8" t="n">
         <v>80.84750809962991</v>
       </c>
       <c r="O492" s="4" t="inlineStr">
@@ -38981,7 +38996,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G493" s="4" t="n">
+      <c r="G493" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H493" s="4" t="inlineStr">
@@ -39014,7 +39029,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N493" s="4" t="n">
+      <c r="N493" s="8" t="n">
         <v>81.3384541743188</v>
       </c>
       <c r="O493" s="4" t="inlineStr">
@@ -39060,7 +39075,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G494" s="4" t="n">
+      <c r="G494" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H494" s="4" t="inlineStr">
@@ -39093,7 +39108,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N494" s="4" t="n">
+      <c r="N494" s="8" t="n">
         <v>81.8081397991543</v>
       </c>
       <c r="O494" s="4" t="inlineStr">
@@ -39139,7 +39154,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G495" s="4" t="n">
+      <c r="G495" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H495" s="4" t="inlineStr">
@@ -39172,7 +39187,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N495" s="4" t="n">
+      <c r="N495" s="8" t="n">
         <v>82.2604998384616</v>
       </c>
       <c r="O495" s="4" t="inlineStr">
@@ -39218,7 +39233,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G496" s="4" t="n">
+      <c r="G496" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H496" s="4" t="inlineStr">
@@ -39251,7 +39266,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N496" s="4" t="n">
+      <c r="N496" s="8" t="n">
         <v>82.6994691565662</v>
       </c>
       <c r="O496" s="4" t="inlineStr">
@@ -39297,7 +39312,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G497" s="4" t="n">
+      <c r="G497" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H497" s="4" t="inlineStr">
@@ -39330,7 +39345,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N497" s="4" t="n">
+      <c r="N497" s="8" t="n">
         <v>83.1289826177933</v>
       </c>
       <c r="O497" s="4" t="inlineStr">
@@ -39376,7 +39391,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G498" s="4" t="n">
+      <c r="G498" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H498" s="4" t="inlineStr">
@@ -39409,7 +39424,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N498" s="4" t="n">
+      <c r="N498" s="8" t="n">
         <v>83.55297508646839</v>
       </c>
       <c r="O498" s="4" t="inlineStr">
@@ -39455,7 +39470,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G499" s="4" t="n">
+      <c r="G499" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H499" s="4" t="inlineStr">
@@ -39488,7 +39503,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N499" s="4" t="n">
+      <c r="N499" s="8" t="n">
         <v>83.97410224303439</v>
       </c>
       <c r="O499" s="4" t="inlineStr">
@@ -39534,7 +39549,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G500" s="4" t="n">
+      <c r="G500" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H500" s="4" t="inlineStr">
@@ -39567,7 +39582,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N500" s="4" t="n">
+      <c r="N500" s="8" t="n">
         <v>84.40920179358289</v>
       </c>
       <c r="O500" s="4" t="inlineStr">
@@ -39613,7 +39628,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G501" s="4" t="n">
+      <c r="G501" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H501" s="4" t="inlineStr">
@@ -39646,7 +39661,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N501" s="4" t="n">
+      <c r="N501" s="8" t="n">
         <v>84.8766356611879</v>
       </c>
       <c r="O501" s="4" t="inlineStr">
@@ -39692,7 +39707,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G502" s="4" t="n">
+      <c r="G502" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H502" s="4" t="inlineStr">
@@ -39725,7 +39740,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N502" s="4" t="n">
+      <c r="N502" s="8" t="n">
         <v>85.3657269170578</v>
       </c>
       <c r="O502" s="4" t="inlineStr">
@@ -39771,7 +39786,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G503" s="4" t="n">
+      <c r="G503" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H503" s="4" t="inlineStr">
@@ -39804,7 +39819,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N503" s="4" t="n">
+      <c r="N503" s="8" t="n">
         <v>85.8624720356125</v>
       </c>
       <c r="O503" s="4" t="inlineStr">
@@ -39850,7 +39865,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G504" s="4" t="n">
+      <c r="G504" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H504" s="4" t="inlineStr">
@@ -39883,7 +39898,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N504" s="4" t="n">
+      <c r="N504" s="8" t="n">
         <v>86.35286749127199</v>
       </c>
       <c r="O504" s="4" t="inlineStr">
@@ -39929,7 +39944,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G505" s="4" t="n">
+      <c r="G505" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H505" s="4" t="inlineStr">
@@ -39962,7 +39977,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N505" s="4" t="n">
+      <c r="N505" s="8" t="n">
         <v>86.8229097584563</v>
       </c>
       <c r="O505" s="4" t="inlineStr">
@@ -40008,7 +40023,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G506" s="4" t="n">
+      <c r="G506" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H506" s="4" t="inlineStr">
@@ -40041,7 +40056,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N506" s="4" t="n">
+      <c r="N506" s="8" t="n">
         <v>87.2585953115854</v>
       </c>
       <c r="O506" s="4" t="inlineStr">
@@ -40087,7 +40102,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G507" s="4" t="n">
+      <c r="G507" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H507" s="4" t="inlineStr">
@@ -40120,7 +40135,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N507" s="4" t="n">
+      <c r="N507" s="8" t="n">
         <v>87.6459206250794</v>
       </c>
       <c r="O507" s="4" t="inlineStr">
@@ -40166,7 +40181,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G508" s="4" t="n">
+      <c r="G508" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H508" s="4" t="inlineStr">
@@ -40199,7 +40214,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N508" s="4" t="n">
+      <c r="N508" s="8" t="n">
         <v>87.97088217335831</v>
       </c>
       <c r="O508" s="4" t="inlineStr">
@@ -40245,7 +40260,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G509" s="4" t="n">
+      <c r="G509" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H509" s="4" t="inlineStr">
@@ -40278,7 +40293,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N509" s="4" t="n">
+      <c r="N509" s="8" t="n">
         <v>88.21947643084199</v>
       </c>
       <c r="O509" s="4" t="inlineStr">
@@ -40324,7 +40339,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G510" s="4" t="n">
+      <c r="G510" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H510" s="4" t="inlineStr">
@@ -40357,7 +40372,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N510" s="4" t="n">
+      <c r="N510" s="8" t="n">
         <v>88.37277412304201</v>
       </c>
       <c r="O510" s="4" t="inlineStr">
@@ -40403,7 +40418,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G511" s="4" t="n">
+      <c r="G511" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H511" s="4" t="inlineStr">
@@ -40436,7 +40451,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N511" s="4" t="n">
+      <c r="N511" s="8" t="n">
         <v>88.45538109510829</v>
       </c>
       <c r="O511" s="4" t="inlineStr">
@@ -40482,7 +40497,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G512" s="4" t="n">
+      <c r="G512" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H512" s="4" t="inlineStr">
@@ -40515,7 +40530,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N512" s="4" t="n">
+      <c r="N512" s="8" t="n">
         <v>88.522274342774</v>
       </c>
       <c r="O512" s="4" t="inlineStr">
@@ -40561,7 +40576,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G513" s="4" t="n">
+      <c r="G513" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H513" s="4" t="inlineStr">
@@ -40594,7 +40609,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N513" s="4" t="n">
+      <c r="N513" s="8" t="n">
         <v>88.5835546444319</v>
       </c>
       <c r="O513" s="4" t="inlineStr">
@@ -40640,7 +40655,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G514" s="4" t="n">
+      <c r="G514" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H514" s="4" t="inlineStr">
@@ -40673,7 +40688,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N514" s="4" t="n">
+      <c r="N514" s="8" t="n">
         <v>88.638673298371</v>
       </c>
       <c r="O514" s="4" t="inlineStr">
@@ -40719,7 +40734,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G515" s="4" t="n">
+      <c r="G515" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H515" s="4" t="inlineStr">
@@ -40752,7 +40767,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N515" s="4" t="n">
+      <c r="N515" s="8" t="n">
         <v>88.6870816028803</v>
       </c>
       <c r="O515" s="4" t="inlineStr">
@@ -40798,7 +40813,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G516" s="4" t="n">
+      <c r="G516" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H516" s="4" t="inlineStr">
@@ -40831,7 +40846,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N516" s="4" t="n">
+      <c r="N516" s="8" t="n">
         <v>88.7282308562487</v>
       </c>
       <c r="O516" s="4" t="inlineStr">
@@ -40877,7 +40892,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G517" s="4" t="n">
+      <c r="G517" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H517" s="4" t="inlineStr">
@@ -40910,7 +40925,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N517" s="4" t="n">
+      <c r="N517" s="8" t="n">
         <v>88.7615723567652</v>
       </c>
       <c r="O517" s="4" t="inlineStr">
@@ -40956,7 +40971,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G518" s="4" t="n">
+      <c r="G518" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H518" s="4" t="inlineStr">
@@ -40989,7 +41004,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N518" s="4" t="n">
+      <c r="N518" s="8" t="n">
         <v>88.7865574027187</v>
       </c>
       <c r="O518" s="4" t="inlineStr">
@@ -41035,7 +41050,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G519" s="4" t="n">
+      <c r="G519" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H519" s="4" t="inlineStr">
@@ -41068,7 +41083,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N519" s="4" t="n">
+      <c r="N519" s="8" t="n">
         <v>88.8026372923982</v>
       </c>
       <c r="O519" s="4" t="inlineStr">
@@ -41114,7 +41129,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G520" s="4" t="n">
+      <c r="G520" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H520" s="4" t="inlineStr">
@@ -41147,7 +41162,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N520" s="4" t="n">
+      <c r="N520" s="8" t="n">
         <v>88.8079278904659</v>
       </c>
       <c r="O520" s="4" t="inlineStr">
@@ -41193,7 +41208,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G521" s="4" t="n">
+      <c r="G521" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H521" s="4" t="inlineStr">
@@ -41226,7 +41241,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N521" s="4" t="n">
+      <c r="N521" s="8" t="n">
         <v>88.8401868543141</v>
       </c>
       <c r="O521" s="4" t="inlineStr">
@@ -41272,7 +41287,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G522" s="4" t="n">
+      <c r="G522" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H522" s="4" t="inlineStr">
@@ -41305,7 +41320,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N522" s="4" t="n">
+      <c r="N522" s="8" t="n">
         <v>88.87868170397211</v>
       </c>
       <c r="O522" s="4" t="inlineStr">
@@ -41351,7 +41366,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G523" s="4" t="n">
+      <c r="G523" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H523" s="4" t="inlineStr">
@@ -41384,7 +41399,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N523" s="4" t="n">
+      <c r="N523" s="8" t="n">
         <v>88.9163913525251</v>
       </c>
       <c r="O523" s="4" t="inlineStr">
@@ -41430,7 +41445,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G524" s="4" t="n">
+      <c r="G524" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H524" s="4" t="inlineStr">
@@ -41463,7 +41478,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N524" s="4" t="n">
+      <c r="N524" s="8" t="n">
         <v>88.95398040792919</v>
       </c>
       <c r="O524" s="4" t="inlineStr">
@@ -41509,7 +41524,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G525" s="4" t="n">
+      <c r="G525" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H525" s="4" t="inlineStr">
@@ -41542,7 +41557,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N525" s="4" t="n">
+      <c r="N525" s="8" t="n">
         <v>88.9914428378712</v>
       </c>
       <c r="O525" s="4" t="inlineStr">
@@ -41588,7 +41603,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G526" s="4" t="n">
+      <c r="G526" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H526" s="4" t="inlineStr">
@@ -41621,7 +41636,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N526" s="4" t="n">
+      <c r="N526" s="8" t="n">
         <v>89.02877261003781</v>
       </c>
       <c r="O526" s="4" t="inlineStr">
@@ -41667,7 +41682,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G527" s="4" t="n">
+      <c r="G527" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H527" s="4" t="inlineStr">
@@ -41700,7 +41715,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N527" s="4" t="n">
+      <c r="N527" s="8" t="n">
         <v>89.0659636921159</v>
       </c>
       <c r="O527" s="4" t="inlineStr">
@@ -41746,7 +41761,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G528" s="4" t="n">
+      <c r="G528" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H528" s="4" t="inlineStr">
@@ -41779,7 +41794,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N528" s="4" t="n">
+      <c r="N528" s="8" t="n">
         <v>89.1030100517924</v>
       </c>
       <c r="O528" s="4" t="inlineStr">
@@ -41825,7 +41840,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G529" s="4" t="n">
+      <c r="G529" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H529" s="4" t="inlineStr">
@@ -41858,7 +41873,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N529" s="4" t="n">
+      <c r="N529" s="8" t="n">
         <v>89.13990565675449</v>
       </c>
       <c r="O529" s="4" t="inlineStr">
@@ -41904,7 +41919,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G530" s="4" t="n">
+      <c r="G530" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H530" s="4" t="inlineStr">
@@ -41937,7 +41952,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N530" s="4" t="n">
+      <c r="N530" s="8" t="n">
         <v>89.1766444746891</v>
       </c>
       <c r="O530" s="4" t="inlineStr">
@@ -41983,7 +41998,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G531" s="4" t="n">
+      <c r="G531" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H531" s="4" t="inlineStr">
@@ -42016,7 +42031,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N531" s="4" t="n">
+      <c r="N531" s="8" t="n">
         <v>89.2132204732836</v>
       </c>
       <c r="O531" s="4" t="inlineStr">
@@ -42062,7 +42077,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G532" s="4" t="n">
+      <c r="G532" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H532" s="4" t="inlineStr">
@@ -42095,7 +42110,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N532" s="4" t="n">
+      <c r="N532" s="8" t="n">
         <v>89.249627620225</v>
       </c>
       <c r="O532" s="4" t="inlineStr">
@@ -42141,7 +42156,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G533" s="4" t="n">
+      <c r="G533" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H533" s="4" t="inlineStr">
@@ -42174,7 +42189,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N533" s="4" t="n">
+      <c r="N533" s="8" t="n">
         <v>89.285859883201</v>
       </c>
       <c r="O533" s="4" t="inlineStr">
@@ -42220,7 +42235,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G534" s="4" t="n">
+      <c r="G534" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H534" s="4" t="inlineStr">
@@ -42253,7 +42268,7 @@
           <t>Población urbana como porcentaje del total</t>
         </is>
       </c>
-      <c r="N534" s="4" t="n">
+      <c r="N534" s="8" t="n">
         <v>89.3219112298988</v>
       </c>
       <c r="O534" s="4" t="inlineStr">
@@ -42358,7 +42373,7 @@
           <t>Número de indicadores</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="7" t="n">
         <v>8</v>
       </c>
     </row>
@@ -42368,7 +42383,7 @@
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="7" t="n">
         <v>528</v>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11380,7 +11380,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -12012,7 +12012,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13276,7 +13276,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14382,7 +14382,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14777,7 +14777,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15804,7 +15804,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16750,7 +16750,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17224,7 +17224,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17540,7 +17540,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17619,7 +17619,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17856,7 +17856,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18093,7 +18093,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18172,7 +18172,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18251,7 +18251,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18409,7 +18409,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18646,7 +18646,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -19041,7 +19041,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19120,7 +19120,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19594,7 +19594,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -20068,7 +20068,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20147,7 +20147,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20226,7 +20226,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20463,7 +20463,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20542,7 +20542,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20621,7 +20621,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20700,7 +20700,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20779,7 +20779,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20858,7 +20858,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -21016,7 +21016,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -21095,7 +21095,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21253,7 +21253,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21411,7 +21411,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21646,7 +21646,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21725,7 +21725,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21804,7 +21804,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21883,7 +21883,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21962,7 +21962,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22199,7 +22199,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22278,7 +22278,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22436,7 +22436,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22515,7 +22515,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22594,7 +22594,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22752,7 +22752,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22910,7 +22910,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -23068,7 +23068,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23147,7 +23147,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23305,7 +23305,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23384,7 +23384,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23463,7 +23463,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23542,7 +23542,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23700,7 +23700,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23858,7 +23858,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23937,7 +23937,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -24016,7 +24016,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24174,7 +24174,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24253,7 +24253,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24332,7 +24332,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24411,7 +24411,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24490,7 +24490,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24727,7 +24727,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24885,7 +24885,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24964,7 +24964,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25201,7 +25201,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25280,7 +25280,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25359,7 +25359,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25517,7 +25517,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25596,7 +25596,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25675,7 +25675,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25754,7 +25754,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25833,7 +25833,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25912,7 +25912,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -26070,7 +26070,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26149,7 +26149,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26228,7 +26228,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26307,7 +26307,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26386,7 +26386,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26465,7 +26465,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26544,7 +26544,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26700,7 +26700,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26856,7 +26856,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26935,7 +26935,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -27172,7 +27172,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -27251,7 +27251,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27330,7 +27330,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27409,7 +27409,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27567,7 +27567,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27646,7 +27646,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27804,7 +27804,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27883,7 +27883,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27962,7 +27962,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -28041,7 +28041,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -28120,7 +28120,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -28278,7 +28278,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28357,7 +28357,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28436,7 +28436,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28515,7 +28515,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28752,7 +28752,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28831,7 +28831,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28910,7 +28910,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -29068,7 +29068,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -29147,7 +29147,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -29305,7 +29305,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29463,7 +29463,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29542,7 +29542,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29621,7 +29621,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29700,7 +29700,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29858,7 +29858,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -30095,7 +30095,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -30253,7 +30253,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -30332,7 +30332,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30411,7 +30411,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30490,7 +30490,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30569,7 +30569,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30648,7 +30648,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30885,7 +30885,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -31043,7 +31043,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -31122,7 +31122,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -31201,7 +31201,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -31280,7 +31280,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31438,7 +31438,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31517,7 +31517,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31596,7 +31596,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31675,7 +31675,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31754,7 +31754,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31833,7 +31833,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31912,7 +31912,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31991,7 +31991,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -32070,7 +32070,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -32149,7 +32149,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32307,7 +32307,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32386,7 +32386,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32465,7 +32465,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32544,7 +32544,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32702,7 +32702,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32939,7 +32939,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -33018,7 +33018,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -33097,7 +33097,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33255,7 +33255,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33334,7 +33334,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33413,7 +33413,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33492,7 +33492,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33571,7 +33571,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33650,7 +33650,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33887,7 +33887,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -34045,7 +34045,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -34124,7 +34124,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -34203,7 +34203,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34282,7 +34282,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34361,7 +34361,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34519,7 +34519,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34677,7 +34677,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34756,7 +34756,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34835,7 +34835,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34914,7 +34914,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34993,7 +34993,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -35072,7 +35072,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -35151,7 +35151,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -35230,7 +35230,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35309,7 +35309,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35388,7 +35388,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35467,7 +35467,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35546,7 +35546,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35704,7 +35704,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35783,7 +35783,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35862,7 +35862,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35941,7 +35941,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -36020,7 +36020,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -36099,7 +36099,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -36178,7 +36178,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36336,7 +36336,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36415,7 +36415,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36573,7 +36573,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36652,7 +36652,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36731,7 +36731,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36810,7 +36810,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36889,7 +36889,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36968,7 +36968,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -37047,7 +37047,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -37126,7 +37126,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -37205,7 +37205,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -37284,7 +37284,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37363,7 +37363,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37442,7 +37442,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37521,7 +37521,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37679,7 +37679,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37758,7 +37758,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37837,7 +37837,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37916,7 +37916,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37995,7 +37995,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -38074,7 +38074,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -38153,7 +38153,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -38232,7 +38232,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -38311,7 +38311,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38390,7 +38390,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38469,7 +38469,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38548,7 +38548,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38627,7 +38627,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38706,7 +38706,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38785,7 +38785,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38864,7 +38864,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38943,7 +38943,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -39022,7 +39022,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -39101,7 +39101,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -39180,7 +39180,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -39259,7 +39259,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39338,7 +39338,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39496,7 +39496,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39575,7 +39575,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39654,7 +39654,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39733,7 +39733,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39812,7 +39812,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39891,7 +39891,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39970,7 +39970,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -40128,7 +40128,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -40207,7 +40207,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -40286,7 +40286,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40444,7 +40444,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40523,7 +40523,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40602,7 +40602,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40681,7 +40681,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40760,7 +40760,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40839,7 +40839,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40918,7 +40918,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40997,7 +40997,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -41076,7 +41076,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -41155,7 +41155,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -41234,7 +41234,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -41313,7 +41313,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41392,7 +41392,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41471,7 +41471,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41550,7 +41550,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41629,7 +41629,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41708,7 +41708,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41787,7 +41787,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41866,7 +41866,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41945,7 +41945,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -42024,7 +42024,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -42103,7 +42103,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -42182,7 +42182,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -42261,7 +42261,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42340,7 +42340,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42425,7 +42425,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11380,7 +11380,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -12012,7 +12012,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13276,7 +13276,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14382,7 +14382,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14777,7 +14777,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15804,7 +15804,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16750,7 +16750,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17224,7 +17224,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17540,7 +17540,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17619,7 +17619,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17856,7 +17856,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18093,7 +18093,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18172,7 +18172,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18251,7 +18251,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18409,7 +18409,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18646,7 +18646,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -19041,7 +19041,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19120,7 +19120,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19594,7 +19594,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -20068,7 +20068,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20147,7 +20147,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20226,7 +20226,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20463,7 +20463,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20542,7 +20542,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20621,7 +20621,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20700,7 +20700,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20779,7 +20779,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20858,7 +20858,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -21016,7 +21016,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -21095,7 +21095,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21253,7 +21253,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21411,7 +21411,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21646,7 +21646,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21725,7 +21725,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21804,7 +21804,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21883,7 +21883,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21962,7 +21962,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22199,7 +22199,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22278,7 +22278,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22436,7 +22436,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22515,7 +22515,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22594,7 +22594,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22752,7 +22752,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22910,7 +22910,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -23068,7 +23068,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23147,7 +23147,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23305,7 +23305,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23384,7 +23384,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23463,7 +23463,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23542,7 +23542,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23700,7 +23700,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23858,7 +23858,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23937,7 +23937,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -24016,7 +24016,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24174,7 +24174,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24253,7 +24253,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24332,7 +24332,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24411,7 +24411,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24490,7 +24490,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24727,7 +24727,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24885,7 +24885,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24964,7 +24964,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25201,7 +25201,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25280,7 +25280,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25359,7 +25359,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25517,7 +25517,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25596,7 +25596,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25675,7 +25675,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25754,7 +25754,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25833,7 +25833,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25912,7 +25912,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -26070,7 +26070,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26149,7 +26149,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26228,7 +26228,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26307,7 +26307,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26386,7 +26386,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26465,7 +26465,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26544,7 +26544,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26700,7 +26700,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26856,7 +26856,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26935,7 +26935,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -27172,7 +27172,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -27251,7 +27251,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27330,7 +27330,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27409,7 +27409,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27567,7 +27567,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27646,7 +27646,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27804,7 +27804,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27883,7 +27883,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27962,7 +27962,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -28041,7 +28041,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -28120,7 +28120,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -28278,7 +28278,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28357,7 +28357,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28436,7 +28436,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28515,7 +28515,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28752,7 +28752,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28831,7 +28831,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28910,7 +28910,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -29068,7 +29068,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -29147,7 +29147,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -29305,7 +29305,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29463,7 +29463,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29542,7 +29542,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29621,7 +29621,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29700,7 +29700,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29858,7 +29858,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -30095,7 +30095,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -30253,7 +30253,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -30332,7 +30332,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30411,7 +30411,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30490,7 +30490,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30569,7 +30569,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30648,7 +30648,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30885,7 +30885,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -31043,7 +31043,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -31122,7 +31122,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -31201,7 +31201,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -31280,7 +31280,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31438,7 +31438,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31517,7 +31517,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31596,7 +31596,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31675,7 +31675,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31754,7 +31754,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31833,7 +31833,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31912,7 +31912,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31991,7 +31991,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -32070,7 +32070,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -32149,7 +32149,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32307,7 +32307,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32386,7 +32386,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32465,7 +32465,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32544,7 +32544,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32702,7 +32702,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32939,7 +32939,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -33018,7 +33018,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -33097,7 +33097,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33255,7 +33255,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33334,7 +33334,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33413,7 +33413,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33492,7 +33492,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33571,7 +33571,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33650,7 +33650,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33887,7 +33887,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -34045,7 +34045,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -34124,7 +34124,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -34203,7 +34203,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34282,7 +34282,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34361,7 +34361,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34519,7 +34519,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34677,7 +34677,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34756,7 +34756,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34835,7 +34835,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34914,7 +34914,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34993,7 +34993,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -35072,7 +35072,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -35151,7 +35151,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -35230,7 +35230,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35309,7 +35309,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35388,7 +35388,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35467,7 +35467,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35546,7 +35546,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35704,7 +35704,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35783,7 +35783,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35862,7 +35862,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35941,7 +35941,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -36020,7 +36020,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -36099,7 +36099,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -36178,7 +36178,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36336,7 +36336,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36415,7 +36415,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36573,7 +36573,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36652,7 +36652,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36731,7 +36731,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36810,7 +36810,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36889,7 +36889,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36968,7 +36968,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -37047,7 +37047,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -37126,7 +37126,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -37205,7 +37205,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -37284,7 +37284,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37363,7 +37363,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37442,7 +37442,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37521,7 +37521,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37679,7 +37679,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37758,7 +37758,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37837,7 +37837,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37916,7 +37916,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37995,7 +37995,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -38074,7 +38074,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -38153,7 +38153,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -38232,7 +38232,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -38311,7 +38311,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38390,7 +38390,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38469,7 +38469,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38548,7 +38548,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38627,7 +38627,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38706,7 +38706,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38785,7 +38785,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38864,7 +38864,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38943,7 +38943,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -39022,7 +39022,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -39101,7 +39101,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -39180,7 +39180,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -39259,7 +39259,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39338,7 +39338,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39496,7 +39496,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39575,7 +39575,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39654,7 +39654,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39733,7 +39733,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39812,7 +39812,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39891,7 +39891,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39970,7 +39970,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -40128,7 +40128,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -40207,7 +40207,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -40286,7 +40286,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40444,7 +40444,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40523,7 +40523,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40602,7 +40602,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40681,7 +40681,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40760,7 +40760,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40839,7 +40839,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40918,7 +40918,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40997,7 +40997,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -41076,7 +41076,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -41155,7 +41155,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -41234,7 +41234,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -41313,7 +41313,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41392,7 +41392,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41471,7 +41471,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41550,7 +41550,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41629,7 +41629,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41708,7 +41708,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41787,7 +41787,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41866,7 +41866,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41945,7 +41945,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -42024,7 +42024,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -42103,7 +42103,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -42182,7 +42182,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -42261,7 +42261,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42340,7 +42340,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42425,7 +42425,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11380,7 +11380,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -12012,7 +12012,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13276,7 +13276,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14382,7 +14382,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14777,7 +14777,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15804,7 +15804,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16750,7 +16750,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17224,7 +17224,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17540,7 +17540,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17619,7 +17619,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17856,7 +17856,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18093,7 +18093,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18172,7 +18172,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18251,7 +18251,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18409,7 +18409,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18646,7 +18646,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -19041,7 +19041,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19120,7 +19120,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19594,7 +19594,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -20068,7 +20068,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20147,7 +20147,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20226,7 +20226,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20463,7 +20463,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20542,7 +20542,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20621,7 +20621,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20700,7 +20700,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20779,7 +20779,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20858,7 +20858,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -21016,7 +21016,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -21095,7 +21095,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21253,7 +21253,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21411,7 +21411,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21646,7 +21646,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21725,7 +21725,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21804,7 +21804,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21883,7 +21883,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21962,7 +21962,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22199,7 +22199,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22278,7 +22278,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22436,7 +22436,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22515,7 +22515,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22594,7 +22594,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22752,7 +22752,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22910,7 +22910,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -23068,7 +23068,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23147,7 +23147,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23305,7 +23305,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23384,7 +23384,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23463,7 +23463,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23542,7 +23542,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23700,7 +23700,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23858,7 +23858,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23937,7 +23937,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -24016,7 +24016,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24174,7 +24174,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24253,7 +24253,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24332,7 +24332,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24411,7 +24411,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24490,7 +24490,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24727,7 +24727,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24885,7 +24885,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24964,7 +24964,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25201,7 +25201,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25280,7 +25280,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25359,7 +25359,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25517,7 +25517,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25596,7 +25596,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25675,7 +25675,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25754,7 +25754,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25833,7 +25833,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25912,7 +25912,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -26070,7 +26070,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26149,7 +26149,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26228,7 +26228,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26307,7 +26307,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26386,7 +26386,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26465,7 +26465,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26544,7 +26544,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26700,7 +26700,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26856,7 +26856,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26935,7 +26935,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -27172,7 +27172,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -27251,7 +27251,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27330,7 +27330,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27409,7 +27409,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27567,7 +27567,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27646,7 +27646,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27804,7 +27804,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27883,7 +27883,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27962,7 +27962,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -28041,7 +28041,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -28120,7 +28120,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -28278,7 +28278,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28357,7 +28357,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28436,7 +28436,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28515,7 +28515,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28752,7 +28752,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28831,7 +28831,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28910,7 +28910,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -29068,7 +29068,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -29147,7 +29147,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -29305,7 +29305,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29463,7 +29463,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29542,7 +29542,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29621,7 +29621,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29700,7 +29700,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29858,7 +29858,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -30095,7 +30095,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -30253,7 +30253,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -30332,7 +30332,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30411,7 +30411,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30490,7 +30490,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30569,7 +30569,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30648,7 +30648,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30885,7 +30885,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -31043,7 +31043,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -31122,7 +31122,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -31201,7 +31201,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -31280,7 +31280,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31438,7 +31438,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31517,7 +31517,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31596,7 +31596,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31675,7 +31675,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31754,7 +31754,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31833,7 +31833,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31912,7 +31912,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31991,7 +31991,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -32070,7 +32070,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -32149,7 +32149,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32307,7 +32307,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32386,7 +32386,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32465,7 +32465,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32544,7 +32544,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32702,7 +32702,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32939,7 +32939,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -33018,7 +33018,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -33097,7 +33097,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33255,7 +33255,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33334,7 +33334,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33413,7 +33413,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33492,7 +33492,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33571,7 +33571,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33650,7 +33650,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33887,7 +33887,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -34045,7 +34045,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -34124,7 +34124,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -34203,7 +34203,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34282,7 +34282,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34361,7 +34361,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34519,7 +34519,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34677,7 +34677,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34756,7 +34756,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34835,7 +34835,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34914,7 +34914,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34993,7 +34993,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -35072,7 +35072,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -35151,7 +35151,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -35230,7 +35230,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35309,7 +35309,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35388,7 +35388,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35467,7 +35467,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35546,7 +35546,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35704,7 +35704,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35783,7 +35783,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35862,7 +35862,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35941,7 +35941,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -36020,7 +36020,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -36099,7 +36099,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -36178,7 +36178,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36336,7 +36336,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36415,7 +36415,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36573,7 +36573,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36652,7 +36652,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36731,7 +36731,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36810,7 +36810,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36889,7 +36889,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36968,7 +36968,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -37047,7 +37047,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -37126,7 +37126,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -37205,7 +37205,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -37284,7 +37284,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37363,7 +37363,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37442,7 +37442,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37521,7 +37521,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37679,7 +37679,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37758,7 +37758,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37837,7 +37837,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37916,7 +37916,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37995,7 +37995,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -38074,7 +38074,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -38153,7 +38153,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -38232,7 +38232,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -38311,7 +38311,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38390,7 +38390,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38469,7 +38469,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38548,7 +38548,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38627,7 +38627,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38706,7 +38706,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38785,7 +38785,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38864,7 +38864,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38943,7 +38943,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -39022,7 +39022,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -39101,7 +39101,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -39180,7 +39180,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -39259,7 +39259,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39338,7 +39338,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39496,7 +39496,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39575,7 +39575,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39654,7 +39654,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39733,7 +39733,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39812,7 +39812,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39891,7 +39891,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39970,7 +39970,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -40128,7 +40128,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -40207,7 +40207,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -40286,7 +40286,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40444,7 +40444,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40523,7 +40523,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40602,7 +40602,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40681,7 +40681,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40760,7 +40760,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40839,7 +40839,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40918,7 +40918,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40997,7 +40997,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -41076,7 +41076,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -41155,7 +41155,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -41234,7 +41234,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -41313,7 +41313,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41392,7 +41392,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41471,7 +41471,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41550,7 +41550,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41629,7 +41629,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41708,7 +41708,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41787,7 +41787,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41866,7 +41866,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41945,7 +41945,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -42024,7 +42024,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -42103,7 +42103,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -42182,7 +42182,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -42261,7 +42261,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42340,7 +42340,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42425,7 +42425,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11380,7 +11380,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -12012,7 +12012,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13276,7 +13276,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14382,7 +14382,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14777,7 +14777,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15804,7 +15804,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16750,7 +16750,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17224,7 +17224,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17540,7 +17540,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17619,7 +17619,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17856,7 +17856,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18093,7 +18093,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18172,7 +18172,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18251,7 +18251,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18409,7 +18409,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18646,7 +18646,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -19041,7 +19041,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19120,7 +19120,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19594,7 +19594,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -20068,7 +20068,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20147,7 +20147,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20226,7 +20226,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20463,7 +20463,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20542,7 +20542,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20621,7 +20621,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20700,7 +20700,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20779,7 +20779,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20858,7 +20858,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -21016,7 +21016,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -21095,7 +21095,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21253,7 +21253,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21411,7 +21411,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21646,7 +21646,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21725,7 +21725,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21804,7 +21804,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21883,7 +21883,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21962,7 +21962,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22199,7 +22199,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22278,7 +22278,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22436,7 +22436,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22515,7 +22515,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22594,7 +22594,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22752,7 +22752,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22910,7 +22910,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -23068,7 +23068,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23147,7 +23147,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23305,7 +23305,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23384,7 +23384,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23463,7 +23463,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23542,7 +23542,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23700,7 +23700,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23858,7 +23858,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23937,7 +23937,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -24016,7 +24016,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24174,7 +24174,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24253,7 +24253,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24332,7 +24332,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24411,7 +24411,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24490,7 +24490,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24727,7 +24727,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24885,7 +24885,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24964,7 +24964,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25201,7 +25201,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25280,7 +25280,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25359,7 +25359,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25517,7 +25517,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25596,7 +25596,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25675,7 +25675,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25754,7 +25754,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25833,7 +25833,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25912,7 +25912,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -26070,7 +26070,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26149,7 +26149,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26228,7 +26228,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26307,7 +26307,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26386,7 +26386,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26465,7 +26465,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26544,7 +26544,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26700,7 +26700,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26856,7 +26856,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26935,7 +26935,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -27172,7 +27172,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -27251,7 +27251,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27330,7 +27330,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27409,7 +27409,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27567,7 +27567,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27646,7 +27646,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27804,7 +27804,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27883,7 +27883,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27962,7 +27962,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -28041,7 +28041,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -28120,7 +28120,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -28278,7 +28278,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28357,7 +28357,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28436,7 +28436,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28515,7 +28515,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28752,7 +28752,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28831,7 +28831,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28910,7 +28910,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -29068,7 +29068,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -29147,7 +29147,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -29305,7 +29305,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29463,7 +29463,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29542,7 +29542,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29621,7 +29621,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29700,7 +29700,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29858,7 +29858,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -30095,7 +30095,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -30253,7 +30253,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -30332,7 +30332,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30411,7 +30411,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30490,7 +30490,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30569,7 +30569,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30648,7 +30648,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30885,7 +30885,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -31043,7 +31043,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -31122,7 +31122,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -31201,7 +31201,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -31280,7 +31280,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31438,7 +31438,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31517,7 +31517,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31596,7 +31596,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31675,7 +31675,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31754,7 +31754,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31833,7 +31833,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31912,7 +31912,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31991,7 +31991,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -32070,7 +32070,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -32149,7 +32149,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32307,7 +32307,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32386,7 +32386,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32465,7 +32465,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32544,7 +32544,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32702,7 +32702,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32939,7 +32939,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -33018,7 +33018,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -33097,7 +33097,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33255,7 +33255,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33334,7 +33334,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33413,7 +33413,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33492,7 +33492,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33571,7 +33571,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33650,7 +33650,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33887,7 +33887,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -34045,7 +34045,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -34124,7 +34124,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -34203,7 +34203,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34282,7 +34282,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34361,7 +34361,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34519,7 +34519,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34677,7 +34677,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34756,7 +34756,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34835,7 +34835,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34914,7 +34914,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34993,7 +34993,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -35072,7 +35072,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -35151,7 +35151,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -35230,7 +35230,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35309,7 +35309,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35388,7 +35388,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35467,7 +35467,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35546,7 +35546,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35704,7 +35704,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35783,7 +35783,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35862,7 +35862,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35941,7 +35941,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -36020,7 +36020,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -36099,7 +36099,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -36178,7 +36178,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36336,7 +36336,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36415,7 +36415,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36573,7 +36573,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36652,7 +36652,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36731,7 +36731,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36810,7 +36810,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36889,7 +36889,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36968,7 +36968,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -37047,7 +37047,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -37126,7 +37126,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -37205,7 +37205,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -37284,7 +37284,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37363,7 +37363,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37442,7 +37442,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37521,7 +37521,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37679,7 +37679,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37758,7 +37758,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37837,7 +37837,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37916,7 +37916,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37995,7 +37995,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -38074,7 +38074,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -38153,7 +38153,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -38232,7 +38232,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -38311,7 +38311,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38390,7 +38390,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38469,7 +38469,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38548,7 +38548,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38627,7 +38627,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38706,7 +38706,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38785,7 +38785,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38864,7 +38864,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38943,7 +38943,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -39022,7 +39022,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -39101,7 +39101,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -39180,7 +39180,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -39259,7 +39259,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39338,7 +39338,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39496,7 +39496,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39575,7 +39575,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39654,7 +39654,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39733,7 +39733,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39812,7 +39812,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39891,7 +39891,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39970,7 +39970,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -40128,7 +40128,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -40207,7 +40207,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -40286,7 +40286,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40444,7 +40444,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40523,7 +40523,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40602,7 +40602,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40681,7 +40681,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40760,7 +40760,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40839,7 +40839,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40918,7 +40918,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40997,7 +40997,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -41076,7 +41076,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -41155,7 +41155,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -41234,7 +41234,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -41313,7 +41313,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41392,7 +41392,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41471,7 +41471,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41550,7 +41550,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41629,7 +41629,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41708,7 +41708,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41787,7 +41787,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41866,7 +41866,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41945,7 +41945,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -42024,7 +42024,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -42103,7 +42103,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -42182,7 +42182,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -42261,7 +42261,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42340,7 +42340,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42425,7 +42425,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11380,7 +11380,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -12012,7 +12012,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13276,7 +13276,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14382,7 +14382,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14777,7 +14777,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15804,7 +15804,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16750,7 +16750,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17224,7 +17224,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17540,7 +17540,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17619,7 +17619,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17856,7 +17856,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18093,7 +18093,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18172,7 +18172,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18251,7 +18251,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18409,7 +18409,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18646,7 +18646,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -19041,7 +19041,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19120,7 +19120,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19594,7 +19594,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -20068,7 +20068,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20147,7 +20147,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20226,7 +20226,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20463,7 +20463,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20542,7 +20542,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20621,7 +20621,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20700,7 +20700,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20779,7 +20779,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20858,7 +20858,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -21016,7 +21016,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -21095,7 +21095,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21253,7 +21253,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21411,7 +21411,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21646,7 +21646,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21725,7 +21725,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21804,7 +21804,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21883,7 +21883,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21962,7 +21962,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22199,7 +22199,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22278,7 +22278,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22436,7 +22436,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22515,7 +22515,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22594,7 +22594,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22752,7 +22752,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22910,7 +22910,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -23068,7 +23068,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23147,7 +23147,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23305,7 +23305,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23384,7 +23384,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23463,7 +23463,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23542,7 +23542,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23700,7 +23700,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23858,7 +23858,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23937,7 +23937,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -24016,7 +24016,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24174,7 +24174,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24253,7 +24253,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24332,7 +24332,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24411,7 +24411,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24490,7 +24490,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24727,7 +24727,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24885,7 +24885,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24964,7 +24964,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25201,7 +25201,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25280,7 +25280,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25359,7 +25359,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25517,7 +25517,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25596,7 +25596,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25675,7 +25675,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25754,7 +25754,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25833,7 +25833,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25912,7 +25912,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -26070,7 +26070,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26149,7 +26149,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26228,7 +26228,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26307,7 +26307,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26386,7 +26386,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26465,7 +26465,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26544,7 +26544,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26700,7 +26700,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26856,7 +26856,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26935,7 +26935,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -27172,7 +27172,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -27251,7 +27251,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27330,7 +27330,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27409,7 +27409,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27567,7 +27567,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27646,7 +27646,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27804,7 +27804,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27883,7 +27883,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27962,7 +27962,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -28041,7 +28041,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -28120,7 +28120,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -28278,7 +28278,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28357,7 +28357,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28436,7 +28436,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28515,7 +28515,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28752,7 +28752,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28831,7 +28831,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28910,7 +28910,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -29068,7 +29068,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -29147,7 +29147,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -29305,7 +29305,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29463,7 +29463,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29542,7 +29542,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29621,7 +29621,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29700,7 +29700,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29858,7 +29858,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -30095,7 +30095,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -30253,7 +30253,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -30332,7 +30332,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30411,7 +30411,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30490,7 +30490,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30569,7 +30569,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30648,7 +30648,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30885,7 +30885,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -31043,7 +31043,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -31122,7 +31122,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -31201,7 +31201,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -31280,7 +31280,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31438,7 +31438,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31517,7 +31517,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31596,7 +31596,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31675,7 +31675,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31754,7 +31754,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31833,7 +31833,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31912,7 +31912,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31991,7 +31991,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -32070,7 +32070,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -32149,7 +32149,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32307,7 +32307,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32386,7 +32386,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32465,7 +32465,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32544,7 +32544,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32702,7 +32702,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32939,7 +32939,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -33018,7 +33018,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -33097,7 +33097,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33255,7 +33255,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33334,7 +33334,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33413,7 +33413,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33492,7 +33492,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33571,7 +33571,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33650,7 +33650,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33887,7 +33887,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -34045,7 +34045,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -34124,7 +34124,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -34203,7 +34203,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34282,7 +34282,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34361,7 +34361,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34519,7 +34519,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34677,7 +34677,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34756,7 +34756,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34835,7 +34835,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34914,7 +34914,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34993,7 +34993,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -35072,7 +35072,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -35151,7 +35151,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -35230,7 +35230,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35309,7 +35309,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35388,7 +35388,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35467,7 +35467,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35546,7 +35546,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35704,7 +35704,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35783,7 +35783,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35862,7 +35862,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35941,7 +35941,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -36020,7 +36020,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -36099,7 +36099,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -36178,7 +36178,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36336,7 +36336,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36415,7 +36415,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36573,7 +36573,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36652,7 +36652,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36731,7 +36731,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36810,7 +36810,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36889,7 +36889,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36968,7 +36968,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -37047,7 +37047,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -37126,7 +37126,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -37205,7 +37205,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -37284,7 +37284,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37363,7 +37363,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37442,7 +37442,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37521,7 +37521,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37679,7 +37679,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37758,7 +37758,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37837,7 +37837,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37916,7 +37916,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37995,7 +37995,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -38074,7 +38074,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -38153,7 +38153,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -38232,7 +38232,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -38311,7 +38311,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38390,7 +38390,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38469,7 +38469,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38548,7 +38548,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38627,7 +38627,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38706,7 +38706,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38785,7 +38785,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38864,7 +38864,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38943,7 +38943,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -39022,7 +39022,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -39101,7 +39101,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -39180,7 +39180,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -39259,7 +39259,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39338,7 +39338,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39496,7 +39496,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39575,7 +39575,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39654,7 +39654,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39733,7 +39733,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39812,7 +39812,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39891,7 +39891,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39970,7 +39970,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -40128,7 +40128,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -40207,7 +40207,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -40286,7 +40286,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40444,7 +40444,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40523,7 +40523,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40602,7 +40602,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40681,7 +40681,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40760,7 +40760,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40839,7 +40839,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40918,7 +40918,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40997,7 +40997,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -41076,7 +41076,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -41155,7 +41155,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -41234,7 +41234,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -41313,7 +41313,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41392,7 +41392,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41471,7 +41471,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41550,7 +41550,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41629,7 +41629,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41708,7 +41708,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41787,7 +41787,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41866,7 +41866,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41945,7 +41945,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -42024,7 +42024,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -42103,7 +42103,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -42182,7 +42182,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -42261,7 +42261,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42340,7 +42340,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42425,7 +42425,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
